--- a/assets/role_action.xlsx
+++ b/assets/role_action.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
     <sheet name="Sheet2" r:id="rId4" sheetId="2"/>
     <sheet name="Sheet3" r:id="rId5" sheetId="3"/>
+    <sheet name="Sheet4" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="279">
   <si>
     <t>action</t>
   </si>
@@ -46,27 +47,27 @@
     <t>Noop</t>
   </si>
   <si>
+    <t>Move: 90</t>
+  </si>
+  <si>
+    <t>Move: 270</t>
+  </si>
+  <si>
+    <t>Move: 180</t>
+  </si>
+  <si>
     <t>Move: 0</t>
   </si>
   <si>
+    <t>Move: 135</t>
+  </si>
+  <si>
     <t>Move: 45</t>
   </si>
   <si>
-    <t>Move: 90</t>
-  </si>
-  <si>
-    <t>Move: 135</t>
-  </si>
-  <si>
-    <t>Move: 180</t>
-  </si>
-  <si>
     <t>Move: 225</t>
   </si>
   <si>
-    <t>Move: 270</t>
-  </si>
-  <si>
     <t>Move: 315</t>
   </si>
   <si>
@@ -448,54 +449,30 @@
     <t>詹姆斯  SF</t>
   </si>
   <si>
+    <t>移动: 90</t>
+  </si>
+  <si>
+    <t>移动: 270</t>
+  </si>
+  <si>
+    <t>移动: 180</t>
+  </si>
+  <si>
     <t>移动: 0</t>
   </si>
   <si>
-    <t>move: 0</t>
+    <t>移动: 135</t>
   </si>
   <si>
     <t>移动: 45</t>
   </si>
   <si>
-    <t>move: 45</t>
-  </si>
-  <si>
-    <t>移动: 90</t>
-  </si>
-  <si>
-    <t>move: 90</t>
-  </si>
-  <si>
-    <t>移动: 135</t>
-  </si>
-  <si>
-    <t>move: 135</t>
-  </si>
-  <si>
-    <t>移动: 180</t>
-  </si>
-  <si>
-    <t>move: 180</t>
-  </si>
-  <si>
     <t>移动: 225</t>
   </si>
   <si>
-    <t>move: 225</t>
-  </si>
-  <si>
-    <t>移动: 270</t>
-  </si>
-  <si>
-    <t>move: 270</t>
-  </si>
-  <si>
     <t>移动: 315</t>
   </si>
   <si>
-    <t>move: 315</t>
-  </si>
-  <si>
     <t>取消技能</t>
   </si>
   <si>
@@ -857,6 +834,24 @@
   </si>
   <si>
     <t>变幻投篮</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Desciption</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>说明</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="false" vertical="center"/>
@@ -1064,6 +1059,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true">
       <alignment wrapText="false" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true">
+      <alignment wrapText="false" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="false" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="false" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true">
+      <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -6320,7 +6327,7 @@
         <v>144</v>
       </c>
       <c r="I3" t="s" s="3">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J3"/>
       <c r="K3"/>
@@ -6339,28 +6346,28 @@
         <v>2.0</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F4" t="s" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G4" t="s" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H4" t="s" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I4" t="s" s="3">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -6379,28 +6386,28 @@
         <v>3.0</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s" s="3">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s" s="3">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s" s="3">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F5" t="s" s="3">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G5" t="s" s="3">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H5" t="s" s="3">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I5" t="s" s="3">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J5"/>
       <c r="K5"/>
@@ -6419,28 +6426,28 @@
         <v>4.0</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s" s="3">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s" s="3">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s" s="3">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F6" t="s" s="3">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G6" t="s" s="3">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H6" t="s" s="3">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I6" t="s" s="3">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -6459,28 +6466,28 @@
         <v>5.0</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F7" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G7" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H7" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I7" t="s" s="3">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J7"/>
       <c r="K7"/>
@@ -6499,28 +6506,28 @@
         <v>6.0</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s" s="3">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s" s="3">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s" s="3">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F8" t="s" s="3">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G8" t="s" s="3">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H8" t="s" s="3">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I8" t="s" s="3">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -6539,28 +6546,28 @@
         <v>7.0</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D9" t="s" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F9" t="s" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G9" t="s" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H9" t="s" s="3">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I9" t="s" s="3">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J9"/>
       <c r="K9"/>
@@ -6579,28 +6586,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E10" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G10" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H10" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="I10" t="s" s="3">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -6619,28 +6626,28 @@
         <v>9.0</v>
       </c>
       <c r="B11" t="s" s="4">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="4">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s" s="4">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F11" t="s" s="4">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G11" t="s" s="4">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H11" t="s" s="4">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="I11" t="s" s="4">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="J11"/>
       <c r="K11"/>
@@ -6659,28 +6666,28 @@
         <v>10.0</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C12" t="s" s="4">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s" s="4">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s" s="4">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F12" t="s" s="4">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G12" t="s" s="4">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H12" t="s" s="4">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I12" t="s" s="4">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -6699,28 +6706,28 @@
         <v>11.0</v>
       </c>
       <c r="B13" t="s" s="4">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s" s="4">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s" s="4">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F13" t="s" s="4">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G13" t="s" s="4">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H13" t="s" s="4">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="I13" t="s" s="4">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J13"/>
       <c r="K13"/>
@@ -6739,28 +6746,28 @@
         <v>12.0</v>
       </c>
       <c r="B14" t="s" s="5">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s" s="5">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s" s="5">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s" s="5">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F14" t="s" s="5">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G14" t="s" s="5">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H14" t="s" s="5">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s" s="5">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="J14"/>
       <c r="K14"/>
@@ -6779,28 +6786,28 @@
         <v>13.0</v>
       </c>
       <c r="B15" t="s" s="5">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D15" t="s" s="5">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E15" t="s" s="5">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F15" t="s" s="5">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G15" t="s" s="5">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H15" t="s" s="5">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I15" t="s" s="5">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="J15"/>
       <c r="K15"/>
@@ -6819,28 +6826,28 @@
         <v>14.0</v>
       </c>
       <c r="B16" t="s" s="5">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C16" t="s" s="5">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D16" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E16" t="s" s="5">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s" s="5">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="G16" t="s" s="5">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="H16" t="s" s="5">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I16" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="J16"/>
       <c r="K16"/>
@@ -6859,28 +6866,28 @@
         <v>15.0</v>
       </c>
       <c r="B17" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s" s="5">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D17" t="s" s="5">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F17" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G17" t="s" s="5">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H17" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="I17" t="s" s="5">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J17"/>
       <c r="K17"/>
@@ -6899,28 +6906,28 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="s" s="5">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s" s="5">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D18" t="s" s="5">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s" s="5">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F18" t="s" s="5">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G18" t="s" s="5">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H18" t="s" s="5">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I18" t="s" s="5">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="J18"/>
       <c r="K18"/>
@@ -6939,28 +6946,28 @@
         <v>17.0</v>
       </c>
       <c r="B19" t="s" s="5">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s" s="5">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D19" t="s" s="5">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s" s="5">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F19" t="s" s="5">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G19" t="s" s="5">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H19" t="s" s="5">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I19" t="s" s="5">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J19"/>
       <c r="K19"/>
@@ -6979,28 +6986,28 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="s" s="5">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E20" t="s" s="5">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F20" t="s" s="5">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G20" t="s" s="5">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H20" t="s" s="5">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I20" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="J20"/>
       <c r="K20"/>
@@ -7019,28 +7026,28 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="s" s="5">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C21" t="s" s="5">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D21" t="s" s="5">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s" s="5">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F21" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="G21" t="s" s="5">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H21" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I21" t="s" s="5">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="J21"/>
       <c r="K21"/>
@@ -7059,28 +7066,28 @@
         <v>20.0</v>
       </c>
       <c r="B22" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s" s="5">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D22" t="s" s="5">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F22" t="s" s="5">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="G22" t="s" s="5">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H22" t="s" s="5">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I22" t="s" s="5">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J22"/>
       <c r="K22"/>
@@ -7099,28 +7106,28 @@
         <v>21.0</v>
       </c>
       <c r="B23" t="s" s="5">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s" s="5">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D23" t="s" s="5">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s" s="5">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F23" t="s" s="5">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G23" t="s" s="5">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H23" t="s" s="5">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s" s="5">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="J23"/>
       <c r="K23"/>
@@ -7139,28 +7146,28 @@
         <v>22.0</v>
       </c>
       <c r="B24" t="s" s="5">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C24" t="s" s="5">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D24" t="s" s="6">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s" s="5">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F24" t="s" s="5">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G24" t="s" s="5">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H24" t="s" s="5">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I24" t="s" s="6">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="J24"/>
       <c r="K24"/>
@@ -7179,28 +7186,28 @@
         <v>23.0</v>
       </c>
       <c r="B25" t="s" s="5">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s" s="6">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D25" t="s" s="6">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s" s="5">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F25" t="s" s="5">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G25" t="s" s="5">
+        <v>170</v>
+      </c>
+      <c r="H25" t="s" s="6">
         <v>178</v>
       </c>
-      <c r="H25" t="s" s="6">
-        <v>186</v>
-      </c>
       <c r="I25" t="s" s="6">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="J25"/>
       <c r="K25"/>
@@ -7219,28 +7226,28 @@
         <v>24.0</v>
       </c>
       <c r="B26" t="s" s="5">
+        <v>173</v>
+      </c>
+      <c r="C26" t="s" s="6">
+        <v>180</v>
+      </c>
+      <c r="D26" t="s" s="6">
         <v>181</v>
       </c>
-      <c r="C26" t="s" s="6">
-        <v>188</v>
-      </c>
-      <c r="D26" t="s" s="6">
-        <v>189</v>
-      </c>
       <c r="E26" t="s" s="5">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F26" t="s" s="6">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G26" t="s" s="5">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="H26" t="s" s="6">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I26" t="s" s="6">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
@@ -7259,28 +7266,28 @@
         <v>25.0</v>
       </c>
       <c r="B27" t="s" s="5">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s" s="6">
+        <v>185</v>
+      </c>
+      <c r="D27" t="s" s="6">
+        <v>186</v>
+      </c>
+      <c r="E27" t="s" s="5">
+        <v>165</v>
+      </c>
+      <c r="F27" t="s" s="6">
+        <v>187</v>
+      </c>
+      <c r="G27" t="s" s="5">
         <v>173</v>
       </c>
-      <c r="C27" t="s" s="6">
-        <v>193</v>
-      </c>
-      <c r="D27" t="s" s="6">
-        <v>194</v>
-      </c>
-      <c r="E27" t="s" s="5">
-        <v>173</v>
-      </c>
-      <c r="F27" t="s" s="6">
-        <v>195</v>
-      </c>
-      <c r="G27" t="s" s="5">
-        <v>181</v>
-      </c>
       <c r="H27" t="s" s="6">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I27" t="s" s="6">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="J27"/>
       <c r="K27"/>
@@ -7299,28 +7306,28 @@
         <v>26.0</v>
       </c>
       <c r="B28" t="s" s="6">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s" s="6">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s" s="6">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E28" t="s" s="6">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F28" t="s" s="6">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G28" t="s" s="6">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H28" t="s" s="6">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I28" t="s" s="6">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="J28"/>
       <c r="K28"/>
@@ -7339,28 +7346,28 @@
         <v>27.0</v>
       </c>
       <c r="B29" t="s" s="6">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C29" t="s" s="6">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D29" t="s" s="6">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E29" t="s" s="6">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F29" t="s" s="6">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G29" t="s" s="6">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="H29" t="s" s="6">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="I29" t="s" s="6">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="J29"/>
       <c r="K29"/>
@@ -7379,28 +7386,28 @@
         <v>28.0</v>
       </c>
       <c r="B30" t="s" s="6">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s" s="6">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D30" t="s" s="6">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E30" t="s" s="6">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F30" t="s" s="6">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G30" t="s" s="6">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="H30" t="s" s="6">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="I30" t="s" s="6">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="J30"/>
       <c r="K30"/>
@@ -7419,28 +7426,28 @@
         <v>29.0</v>
       </c>
       <c r="B31" t="s" s="6">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C31" t="s" s="6">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s" s="6">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E31" t="s" s="6">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F31" t="s" s="6">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G31" t="s" s="6">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="H31" t="s" s="6">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I31" t="s" s="6">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="J31"/>
       <c r="K31"/>
@@ -7459,28 +7466,28 @@
         <v>30.0</v>
       </c>
       <c r="B32" t="s" s="6">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C32" t="s" s="6">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D32" t="s" s="6">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E32" t="s" s="6">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F32" t="s" s="6">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G32" t="s" s="6">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="H32" t="s" s="6">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I32" t="s" s="6">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="J32"/>
       <c r="K32"/>
@@ -7499,26 +7506,26 @@
         <v>31.0</v>
       </c>
       <c r="B33" t="s" s="6">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C33" t="s" s="6">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" t="s" s="6">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F33" t="s" s="6">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="G33" t="s" s="6">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="H33" t="s" s="6">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="I33" t="s" s="6">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="J33"/>
       <c r="K33"/>
@@ -7537,26 +7544,26 @@
         <v>32.0</v>
       </c>
       <c r="B34" t="s" s="6">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s" s="6">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" t="s" s="6">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="F34" t="s" s="6">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="G34" t="s" s="6">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="H34" t="s" s="6">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="I34" t="s" s="6">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="J34"/>
       <c r="K34"/>
@@ -7575,24 +7582,24 @@
         <v>33.0</v>
       </c>
       <c r="B35" t="s" s="6">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s" s="6">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" t="s" s="6">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" t="s" s="6">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="H35" t="s" s="6">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I35" t="s" s="6">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J35"/>
       <c r="K35"/>
@@ -7611,24 +7618,24 @@
         <v>34.0</v>
       </c>
       <c r="B36" t="s" s="6">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C36" t="s" s="6">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" t="s" s="6">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" t="s" s="6">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H36" t="s" s="6">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I36" t="s" s="6">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="J36"/>
       <c r="K36"/>
@@ -7647,22 +7654,22 @@
         <v>35.0</v>
       </c>
       <c r="B37" t="s" s="6">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C37" t="s" s="6">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" t="s" s="6">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" t="s" s="6">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" t="s" s="6">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="J37"/>
       <c r="K37"/>
@@ -7681,22 +7688,22 @@
         <v>36.0</v>
       </c>
       <c r="B38" t="s" s="6">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C38" t="s" s="6">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" t="s" s="6">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" t="s" s="6">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" t="s" s="6">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="J38"/>
       <c r="K38"/>
@@ -7715,14 +7722,14 @@
         <v>37.0</v>
       </c>
       <c r="B39" t="s" s="6">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" t="s" s="6">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -7743,14 +7750,14 @@
         <v>38.0</v>
       </c>
       <c r="B40" t="s" s="6">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" t="s" s="6">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -7771,14 +7778,14 @@
         <v>39.0</v>
       </c>
       <c r="B41" t="s" s="6">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" t="s" s="6">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -7804,7 +7811,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" t="s" s="6">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -11325,13 +11332,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T200"/>
+  <dimension ref="A1:T201"/>
   <sheetFormatPr defaultRowHeight="19.5" baseColWidth="14" customHeight="true"/>
+  <cols>
+    <col min="2" max="2" width="43.0" customWidth="true"/>
+    <col min="3" max="3" width="71.0" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="true">
-      <c r="A1"/>
-      <c r="B1"/>
-      <c r="C1"/>
+      <c r="A1" t="s" s="12">
+        <v>273</v>
+      </c>
+      <c r="B1" t="s" s="9">
+        <v>274</v>
+      </c>
+      <c r="C1" t="s" s="11">
+        <v>275</v>
+      </c>
       <c r="D1"/>
       <c r="E1"/>
       <c r="F1"/>
@@ -11351,9 +11368,13 @@
       <c r="T1"/>
     </row>
     <row r="2" ht="19.5" customHeight="true">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2"/>
+      <c r="A2" t="s" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s" s="9">
+        <v>53</v>
+      </c>
+      <c r="C2" s="10"/>
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2"/>
@@ -11373,9 +11394,11 @@
       <c r="T2"/>
     </row>
     <row r="3" ht="19.5" customHeight="true">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3"/>
+      <c r="A3" s="10"/>
+      <c r="B3" t="s" s="9">
+        <v>61</v>
+      </c>
+      <c r="C3" s="10"/>
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3"/>
@@ -11395,9 +11418,11 @@
       <c r="T3"/>
     </row>
     <row r="4" ht="19.5" customHeight="true">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4"/>
+      <c r="A4" s="10"/>
+      <c r="B4" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="C4" s="10"/>
       <c r="D4"/>
       <c r="E4"/>
       <c r="F4"/>
@@ -11417,9 +11442,11 @@
       <c r="T4"/>
     </row>
     <row r="5" ht="19.5" customHeight="true">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5"/>
+      <c r="A5" s="10"/>
+      <c r="B5" t="s" s="9">
+        <v>77</v>
+      </c>
+      <c r="C5" s="10"/>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5"/>
@@ -11439,9 +11466,11 @@
       <c r="T5"/>
     </row>
     <row r="6" ht="19.5" customHeight="true">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
+      <c r="A6" s="10"/>
+      <c r="B6" t="s" s="9">
+        <v>84</v>
+      </c>
+      <c r="C6" s="10"/>
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
@@ -11461,9 +11490,11 @@
       <c r="T6"/>
     </row>
     <row r="7" ht="19.5" customHeight="true">
-      <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7"/>
+      <c r="A7" s="10"/>
+      <c r="B7" t="s" s="9">
+        <v>92</v>
+      </c>
+      <c r="C7" s="10"/>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -11483,9 +11514,11 @@
       <c r="T7"/>
     </row>
     <row r="8" ht="19.5" customHeight="true">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="C8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" t="s" s="9">
+        <v>99</v>
+      </c>
+      <c r="C8" s="10"/>
       <c r="D8"/>
       <c r="E8"/>
       <c r="F8"/>
@@ -11505,9 +11538,11 @@
       <c r="T8"/>
     </row>
     <row r="9" ht="19.5" customHeight="true">
-      <c r="A9"/>
-      <c r="B9"/>
-      <c r="C9"/>
+      <c r="A9" s="10"/>
+      <c r="B9" t="s" s="9">
+        <v>106</v>
+      </c>
+      <c r="C9" s="10"/>
       <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
@@ -11527,9 +11562,11 @@
       <c r="T9"/>
     </row>
     <row r="10" ht="19.5" customHeight="true">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="C10"/>
+      <c r="A10" s="10"/>
+      <c r="B10" t="s" s="9">
+        <v>112</v>
+      </c>
+      <c r="C10" s="10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
@@ -11549,9 +11586,11 @@
       <c r="T10"/>
     </row>
     <row r="11" ht="19.5" customHeight="true">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
+      <c r="A11" s="10"/>
+      <c r="B11" t="s" s="9">
+        <v>118</v>
+      </c>
+      <c r="C11" s="10"/>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11"/>
@@ -11571,9 +11610,11 @@
       <c r="T11"/>
     </row>
     <row r="12" ht="19.5" customHeight="true">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="C12"/>
+      <c r="A12" s="10"/>
+      <c r="B12" t="s" s="9">
+        <v>123</v>
+      </c>
+      <c r="C12" s="10"/>
       <c r="D12"/>
       <c r="E12"/>
       <c r="F12"/>
@@ -11593,9 +11634,11 @@
       <c r="T12"/>
     </row>
     <row r="13" ht="19.5" customHeight="true">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
+      <c r="A13" s="10"/>
+      <c r="B13" t="s" s="9">
+        <v>128</v>
+      </c>
+      <c r="C13" s="10"/>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
@@ -11615,9 +11658,11 @@
       <c r="T13"/>
     </row>
     <row r="14" ht="19.5" customHeight="true">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
+      <c r="A14" s="10"/>
+      <c r="B14" t="s" s="9">
+        <v>130</v>
+      </c>
+      <c r="C14" s="10"/>
       <c r="D14"/>
       <c r="E14"/>
       <c r="F14"/>
@@ -11637,9 +11682,11 @@
       <c r="T14"/>
     </row>
     <row r="15" ht="19.5" customHeight="true">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
+      <c r="A15" s="10"/>
+      <c r="B15" t="s" s="9">
+        <v>132</v>
+      </c>
+      <c r="C15" s="10"/>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15"/>
@@ -11659,8 +11706,4480 @@
       <c r="T15"/>
     </row>
     <row r="16" ht="19.5" customHeight="true">
-      <c r="A16"/>
-      <c r="B16"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="true">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="true">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="true">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="true">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="true">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+    </row>
+    <row r="22" ht="19.5" customHeight="true">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+    </row>
+    <row r="23" ht="19.5" customHeight="true">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="true">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+      <c r="S24"/>
+      <c r="T24"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="true">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+      <c r="S25"/>
+      <c r="T25"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="true">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="true">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="true">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="true">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="true">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="true">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="true">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+      <c r="S32"/>
+      <c r="T32"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="true">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+      <c r="S33"/>
+      <c r="T33"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="true">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="true">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+      <c r="S35"/>
+      <c r="T35"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="true">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+      <c r="S36"/>
+      <c r="T36"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="true">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="true">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38"/>
+      <c r="T38"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="true">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="true">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="true">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="true">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="true">
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+      <c r="S43"/>
+      <c r="T43"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="true">
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+      <c r="S44"/>
+      <c r="T44"/>
+    </row>
+    <row r="45" ht="19.5" customHeight="true">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+      <c r="S45"/>
+      <c r="T45"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="true">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="true">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="true">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
+      <c r="Q48"/>
+      <c r="R48"/>
+      <c r="S48"/>
+      <c r="T48"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="true">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
+      <c r="P49"/>
+      <c r="Q49"/>
+      <c r="R49"/>
+      <c r="S49"/>
+      <c r="T49"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="true">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
+      <c r="P50"/>
+      <c r="Q50"/>
+      <c r="R50"/>
+      <c r="S50"/>
+      <c r="T50"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="true">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
+      <c r="P51"/>
+      <c r="Q51"/>
+      <c r="R51"/>
+      <c r="S51"/>
+      <c r="T51"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="true">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="R52"/>
+      <c r="S52"/>
+      <c r="T52"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="true">
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+      <c r="R53"/>
+      <c r="S53"/>
+      <c r="T53"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="true">
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+      <c r="S54"/>
+      <c r="T54"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="true">
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="R55"/>
+      <c r="S55"/>
+      <c r="T55"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="true">
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+      <c r="S56"/>
+      <c r="T56"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="true">
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57"/>
+      <c r="S57"/>
+      <c r="T57"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="true">
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+      <c r="S58"/>
+      <c r="T58"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="true">
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="R59"/>
+      <c r="S59"/>
+      <c r="T59"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="true">
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="M60"/>
+      <c r="N60"/>
+      <c r="O60"/>
+      <c r="P60"/>
+      <c r="Q60"/>
+      <c r="R60"/>
+      <c r="S60"/>
+      <c r="T60"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="true">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+      <c r="R61"/>
+      <c r="S61"/>
+      <c r="T61"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="true">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="P62"/>
+      <c r="Q62"/>
+      <c r="R62"/>
+      <c r="S62"/>
+      <c r="T62"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="true">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="M63"/>
+      <c r="N63"/>
+      <c r="O63"/>
+      <c r="P63"/>
+      <c r="Q63"/>
+      <c r="R63"/>
+      <c r="S63"/>
+      <c r="T63"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="true">
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="P64"/>
+      <c r="Q64"/>
+      <c r="R64"/>
+      <c r="S64"/>
+      <c r="T64"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="true">
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="Q65"/>
+      <c r="R65"/>
+      <c r="S65"/>
+      <c r="T65"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="true">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
+      <c r="M66"/>
+      <c r="N66"/>
+      <c r="O66"/>
+      <c r="P66"/>
+      <c r="Q66"/>
+      <c r="R66"/>
+      <c r="S66"/>
+      <c r="T66"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="true">
+      <c r="A67" s="10"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+      <c r="R67"/>
+      <c r="S67"/>
+      <c r="T67"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="true">
+      <c r="A68" s="10"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="M68"/>
+      <c r="N68"/>
+      <c r="O68"/>
+      <c r="P68"/>
+      <c r="Q68"/>
+      <c r="R68"/>
+      <c r="S68"/>
+      <c r="T68"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="true">
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="M69"/>
+      <c r="N69"/>
+      <c r="O69"/>
+      <c r="P69"/>
+      <c r="Q69"/>
+      <c r="R69"/>
+      <c r="S69"/>
+      <c r="T69"/>
+    </row>
+    <row r="70" ht="19.5" customHeight="true">
+      <c r="A70" s="10"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="M70"/>
+      <c r="N70"/>
+      <c r="O70"/>
+      <c r="P70"/>
+      <c r="Q70"/>
+      <c r="R70"/>
+      <c r="S70"/>
+      <c r="T70"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="true">
+      <c r="A71" s="10"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+      <c r="R71"/>
+      <c r="S71"/>
+      <c r="T71"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="true">
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72"/>
+      <c r="T72"/>
+    </row>
+    <row r="73" ht="19.5" customHeight="true">
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="O73"/>
+      <c r="P73"/>
+      <c r="Q73"/>
+      <c r="R73"/>
+      <c r="S73"/>
+      <c r="T73"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="true">
+      <c r="A74" s="10"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+      <c r="N74"/>
+      <c r="O74"/>
+      <c r="P74"/>
+      <c r="Q74"/>
+      <c r="R74"/>
+      <c r="S74"/>
+      <c r="T74"/>
+    </row>
+    <row r="75" ht="19.5" customHeight="true">
+      <c r="A75" s="10"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
+      <c r="N75"/>
+      <c r="O75"/>
+      <c r="P75"/>
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="S75"/>
+      <c r="T75"/>
+    </row>
+    <row r="76" ht="19.5" customHeight="true">
+      <c r="A76" s="10"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="M76"/>
+      <c r="N76"/>
+      <c r="O76"/>
+      <c r="P76"/>
+      <c r="Q76"/>
+      <c r="R76"/>
+      <c r="S76"/>
+      <c r="T76"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="true">
+      <c r="A77" s="10"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="S77"/>
+      <c r="T77"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="true">
+      <c r="A78" s="10"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
+      <c r="I78"/>
+      <c r="J78"/>
+      <c r="K78"/>
+      <c r="L78"/>
+      <c r="M78"/>
+      <c r="N78"/>
+      <c r="O78"/>
+      <c r="P78"/>
+      <c r="Q78"/>
+      <c r="R78"/>
+      <c r="S78"/>
+      <c r="T78"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="true">
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79"/>
+      <c r="I79"/>
+      <c r="J79"/>
+      <c r="K79"/>
+      <c r="L79"/>
+      <c r="M79"/>
+      <c r="N79"/>
+      <c r="O79"/>
+      <c r="P79"/>
+      <c r="Q79"/>
+      <c r="R79"/>
+      <c r="S79"/>
+      <c r="T79"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="true">
+      <c r="A80" s="10"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
+      <c r="K80"/>
+      <c r="L80"/>
+      <c r="M80"/>
+      <c r="N80"/>
+      <c r="O80"/>
+      <c r="P80"/>
+      <c r="Q80"/>
+      <c r="R80"/>
+      <c r="S80"/>
+      <c r="T80"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="true">
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81"/>
+      <c r="T81"/>
+    </row>
+    <row r="82" ht="19.5" customHeight="true">
+      <c r="A82" s="10"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
+      <c r="L82"/>
+      <c r="M82"/>
+      <c r="N82"/>
+      <c r="O82"/>
+      <c r="P82"/>
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="S82"/>
+      <c r="T82"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="true">
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="10"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83"/>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
+      <c r="N83"/>
+      <c r="O83"/>
+      <c r="P83"/>
+      <c r="Q83"/>
+      <c r="R83"/>
+      <c r="S83"/>
+      <c r="T83"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="true">
+      <c r="A84" s="10"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="10"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
+      <c r="L84"/>
+      <c r="M84"/>
+      <c r="N84"/>
+      <c r="O84"/>
+      <c r="P84"/>
+      <c r="Q84"/>
+      <c r="R84"/>
+      <c r="S84"/>
+      <c r="T84"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="true">
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+      <c r="I85"/>
+      <c r="J85"/>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85"/>
+      <c r="N85"/>
+      <c r="O85"/>
+      <c r="P85"/>
+      <c r="Q85"/>
+      <c r="R85"/>
+      <c r="S85"/>
+      <c r="T85"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="true">
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
+      <c r="K86"/>
+      <c r="L86"/>
+      <c r="M86"/>
+      <c r="N86"/>
+      <c r="O86"/>
+      <c r="P86"/>
+      <c r="Q86"/>
+      <c r="R86"/>
+      <c r="S86"/>
+      <c r="T86"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="true">
+      <c r="A87" s="10"/>
+      <c r="B87" s="10"/>
+      <c r="C87" s="10"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+      <c r="M87"/>
+      <c r="N87"/>
+      <c r="O87"/>
+      <c r="P87"/>
+      <c r="Q87"/>
+      <c r="R87"/>
+      <c r="S87"/>
+      <c r="T87"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="true">
+      <c r="A88" s="10"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="10"/>
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+      <c r="K88"/>
+      <c r="L88"/>
+      <c r="M88"/>
+      <c r="N88"/>
+      <c r="O88"/>
+      <c r="P88"/>
+      <c r="Q88"/>
+      <c r="R88"/>
+      <c r="S88"/>
+      <c r="T88"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="true">
+      <c r="A89" s="10"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="10"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
+      <c r="I89"/>
+      <c r="J89"/>
+      <c r="K89"/>
+      <c r="L89"/>
+      <c r="M89"/>
+      <c r="N89"/>
+      <c r="O89"/>
+      <c r="P89"/>
+      <c r="Q89"/>
+      <c r="R89"/>
+      <c r="S89"/>
+      <c r="T89"/>
+    </row>
+    <row r="90" ht="19.5" customHeight="true">
+      <c r="A90" s="10"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="10"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="I90"/>
+      <c r="J90"/>
+      <c r="K90"/>
+      <c r="L90"/>
+      <c r="M90"/>
+      <c r="N90"/>
+      <c r="O90"/>
+      <c r="P90"/>
+      <c r="Q90"/>
+      <c r="R90"/>
+      <c r="S90"/>
+      <c r="T90"/>
+    </row>
+    <row r="91" ht="19.5" customHeight="true">
+      <c r="A91" s="10"/>
+      <c r="B91" s="10"/>
+      <c r="C91" s="10"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
+      <c r="N91"/>
+      <c r="O91"/>
+      <c r="P91"/>
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="S91"/>
+      <c r="T91"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="true">
+      <c r="A92" s="10"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="10"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="I92"/>
+      <c r="J92"/>
+      <c r="K92"/>
+      <c r="L92"/>
+      <c r="M92"/>
+      <c r="N92"/>
+      <c r="O92"/>
+      <c r="P92"/>
+      <c r="Q92"/>
+      <c r="R92"/>
+      <c r="S92"/>
+      <c r="T92"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="true">
+      <c r="A93" s="10"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="H93"/>
+      <c r="I93"/>
+      <c r="J93"/>
+      <c r="K93"/>
+      <c r="L93"/>
+      <c r="M93"/>
+      <c r="N93"/>
+      <c r="O93"/>
+      <c r="P93"/>
+      <c r="Q93"/>
+      <c r="R93"/>
+      <c r="S93"/>
+      <c r="T93"/>
+    </row>
+    <row r="94" ht="19.5" customHeight="true">
+      <c r="A94" s="10"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
+      <c r="K94"/>
+      <c r="L94"/>
+      <c r="M94"/>
+      <c r="N94"/>
+      <c r="O94"/>
+      <c r="P94"/>
+      <c r="Q94"/>
+      <c r="R94"/>
+      <c r="S94"/>
+      <c r="T94"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="true">
+      <c r="A95" s="10"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95"/>
+      <c r="I95"/>
+      <c r="J95"/>
+      <c r="K95"/>
+      <c r="L95"/>
+      <c r="M95"/>
+      <c r="N95"/>
+      <c r="O95"/>
+      <c r="P95"/>
+      <c r="Q95"/>
+      <c r="R95"/>
+      <c r="S95"/>
+      <c r="T95"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="true">
+      <c r="A96" s="10"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="10"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="H96"/>
+      <c r="I96"/>
+      <c r="J96"/>
+      <c r="K96"/>
+      <c r="L96"/>
+      <c r="M96"/>
+      <c r="N96"/>
+      <c r="O96"/>
+      <c r="P96"/>
+      <c r="Q96"/>
+      <c r="R96"/>
+      <c r="S96"/>
+      <c r="T96"/>
+    </row>
+    <row r="97" ht="19.5" customHeight="true">
+      <c r="A97" s="10"/>
+      <c r="B97" s="10"/>
+      <c r="C97" s="10"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97"/>
+      <c r="I97"/>
+      <c r="J97"/>
+      <c r="K97"/>
+      <c r="L97"/>
+      <c r="M97"/>
+      <c r="N97"/>
+      <c r="O97"/>
+      <c r="P97"/>
+      <c r="Q97"/>
+      <c r="R97"/>
+      <c r="S97"/>
+      <c r="T97"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="true">
+      <c r="A98" s="10"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="H98"/>
+      <c r="I98"/>
+      <c r="J98"/>
+      <c r="K98"/>
+      <c r="L98"/>
+      <c r="M98"/>
+      <c r="N98"/>
+      <c r="O98"/>
+      <c r="P98"/>
+      <c r="Q98"/>
+      <c r="R98"/>
+      <c r="S98"/>
+      <c r="T98"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="true">
+      <c r="A99" s="10"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="10"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99"/>
+      <c r="M99"/>
+      <c r="N99"/>
+      <c r="O99"/>
+      <c r="P99"/>
+      <c r="Q99"/>
+      <c r="R99"/>
+      <c r="S99"/>
+      <c r="T99"/>
+    </row>
+    <row r="100" ht="19.5" customHeight="true">
+      <c r="A100" s="10"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="10"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+      <c r="I100"/>
+      <c r="J100"/>
+      <c r="K100"/>
+      <c r="L100"/>
+      <c r="M100"/>
+      <c r="N100"/>
+      <c r="O100"/>
+      <c r="P100"/>
+      <c r="Q100"/>
+      <c r="R100"/>
+      <c r="S100"/>
+      <c r="T100"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="true">
+      <c r="A101" s="10"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="10"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="true">
+      <c r="A102" s="10"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="10"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
+      <c r="M102"/>
+      <c r="N102"/>
+      <c r="O102"/>
+      <c r="P102"/>
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="S102"/>
+      <c r="T102"/>
+    </row>
+    <row r="103" ht="19.5" customHeight="true">
+      <c r="A103" s="10"/>
+      <c r="B103" s="10"/>
+      <c r="C103" s="10"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
+      <c r="K103"/>
+      <c r="L103"/>
+      <c r="M103"/>
+      <c r="N103"/>
+      <c r="O103"/>
+      <c r="P103"/>
+      <c r="Q103"/>
+      <c r="R103"/>
+      <c r="S103"/>
+      <c r="T103"/>
+    </row>
+    <row r="104" ht="19.5" customHeight="true">
+      <c r="A104" s="10"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="10"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
+      <c r="K104"/>
+      <c r="L104"/>
+      <c r="M104"/>
+      <c r="N104"/>
+      <c r="O104"/>
+      <c r="P104"/>
+      <c r="Q104"/>
+      <c r="R104"/>
+      <c r="S104"/>
+      <c r="T104"/>
+    </row>
+    <row r="105" ht="19.5" customHeight="true">
+      <c r="A105" s="10"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="10"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105"/>
+      <c r="K105"/>
+      <c r="L105"/>
+      <c r="M105"/>
+      <c r="N105"/>
+      <c r="O105"/>
+      <c r="P105"/>
+      <c r="Q105"/>
+      <c r="R105"/>
+      <c r="S105"/>
+      <c r="T105"/>
+    </row>
+    <row r="106" ht="19.5" customHeight="true">
+      <c r="A106" s="10"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="10"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106"/>
+      <c r="K106"/>
+      <c r="L106"/>
+      <c r="M106"/>
+      <c r="N106"/>
+      <c r="O106"/>
+      <c r="P106"/>
+      <c r="Q106"/>
+      <c r="R106"/>
+      <c r="S106"/>
+      <c r="T106"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="true">
+      <c r="A107" s="10"/>
+      <c r="B107" s="10"/>
+      <c r="C107" s="10"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
+      <c r="K107"/>
+      <c r="L107"/>
+      <c r="M107"/>
+      <c r="N107"/>
+      <c r="O107"/>
+      <c r="P107"/>
+      <c r="Q107"/>
+      <c r="R107"/>
+      <c r="S107"/>
+      <c r="T107"/>
+    </row>
+    <row r="108" ht="19.5" customHeight="true">
+      <c r="A108" s="10"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="10"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+      <c r="K108"/>
+      <c r="L108"/>
+      <c r="M108"/>
+      <c r="N108"/>
+      <c r="O108"/>
+      <c r="P108"/>
+      <c r="Q108"/>
+      <c r="R108"/>
+      <c r="S108"/>
+      <c r="T108"/>
+    </row>
+    <row r="109" ht="19.5" customHeight="true">
+      <c r="A109" s="10"/>
+      <c r="B109" s="10"/>
+      <c r="C109" s="10"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109"/>
+      <c r="K109"/>
+      <c r="L109"/>
+      <c r="M109"/>
+      <c r="N109"/>
+      <c r="O109"/>
+      <c r="P109"/>
+      <c r="Q109"/>
+      <c r="R109"/>
+      <c r="S109"/>
+      <c r="T109"/>
+    </row>
+    <row r="110" ht="19.5" customHeight="true">
+      <c r="A110" s="10"/>
+      <c r="B110" s="10"/>
+      <c r="C110" s="10"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+      <c r="L110"/>
+      <c r="M110"/>
+      <c r="N110"/>
+      <c r="O110"/>
+      <c r="P110"/>
+      <c r="Q110"/>
+      <c r="R110"/>
+      <c r="S110"/>
+      <c r="T110"/>
+    </row>
+    <row r="111" ht="19.5" customHeight="true">
+      <c r="A111" s="10"/>
+      <c r="B111" s="10"/>
+      <c r="C111" s="10"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+      <c r="L111"/>
+      <c r="M111"/>
+      <c r="N111"/>
+      <c r="O111"/>
+      <c r="P111"/>
+      <c r="Q111"/>
+      <c r="R111"/>
+      <c r="S111"/>
+      <c r="T111"/>
+    </row>
+    <row r="112" ht="19.5" customHeight="true">
+      <c r="A112" s="10"/>
+      <c r="B112" s="10"/>
+      <c r="C112" s="10"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="I112"/>
+      <c r="J112"/>
+      <c r="K112"/>
+      <c r="L112"/>
+      <c r="M112"/>
+      <c r="N112"/>
+      <c r="O112"/>
+      <c r="P112"/>
+      <c r="Q112"/>
+      <c r="R112"/>
+      <c r="S112"/>
+      <c r="T112"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="true">
+      <c r="A113" s="10"/>
+      <c r="B113" s="10"/>
+      <c r="C113" s="10"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+      <c r="L113"/>
+      <c r="M113"/>
+      <c r="N113"/>
+      <c r="O113"/>
+      <c r="P113"/>
+      <c r="Q113"/>
+      <c r="R113"/>
+      <c r="S113"/>
+      <c r="T113"/>
+    </row>
+    <row r="114" ht="19.5" customHeight="true">
+      <c r="A114" s="10"/>
+      <c r="B114" s="10"/>
+      <c r="C114" s="10"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
+      <c r="K114"/>
+      <c r="L114"/>
+      <c r="M114"/>
+      <c r="N114"/>
+      <c r="O114"/>
+      <c r="P114"/>
+      <c r="Q114"/>
+      <c r="R114"/>
+      <c r="S114"/>
+      <c r="T114"/>
+    </row>
+    <row r="115" ht="19.5" customHeight="true">
+      <c r="A115" s="10"/>
+      <c r="B115" s="10"/>
+      <c r="C115" s="10"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115"/>
+      <c r="K115"/>
+      <c r="L115"/>
+      <c r="M115"/>
+      <c r="N115"/>
+      <c r="O115"/>
+      <c r="P115"/>
+      <c r="Q115"/>
+      <c r="R115"/>
+      <c r="S115"/>
+      <c r="T115"/>
+    </row>
+    <row r="116" ht="19.5" customHeight="true">
+      <c r="A116" s="10"/>
+      <c r="B116" s="10"/>
+      <c r="C116" s="10"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116"/>
+      <c r="K116"/>
+      <c r="L116"/>
+      <c r="M116"/>
+      <c r="N116"/>
+      <c r="O116"/>
+      <c r="P116"/>
+      <c r="Q116"/>
+      <c r="R116"/>
+      <c r="S116"/>
+      <c r="T116"/>
+    </row>
+    <row r="117" ht="19.5" customHeight="true">
+      <c r="A117" s="10"/>
+      <c r="B117" s="10"/>
+      <c r="C117" s="10"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
+      <c r="K117"/>
+      <c r="L117"/>
+      <c r="M117"/>
+      <c r="N117"/>
+      <c r="O117"/>
+      <c r="P117"/>
+      <c r="Q117"/>
+      <c r="R117"/>
+      <c r="S117"/>
+      <c r="T117"/>
+    </row>
+    <row r="118" ht="19.5" customHeight="true">
+      <c r="A118" s="10"/>
+      <c r="B118" s="10"/>
+      <c r="C118" s="10"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
+      <c r="K118"/>
+      <c r="L118"/>
+      <c r="M118"/>
+      <c r="N118"/>
+      <c r="O118"/>
+      <c r="P118"/>
+      <c r="Q118"/>
+      <c r="R118"/>
+      <c r="S118"/>
+      <c r="T118"/>
+    </row>
+    <row r="119" ht="19.5" customHeight="true">
+      <c r="A119" s="10"/>
+      <c r="B119" s="10"/>
+      <c r="C119" s="10"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
+      <c r="K119"/>
+      <c r="L119"/>
+      <c r="M119"/>
+      <c r="N119"/>
+      <c r="O119"/>
+      <c r="P119"/>
+      <c r="Q119"/>
+      <c r="R119"/>
+      <c r="S119"/>
+      <c r="T119"/>
+    </row>
+    <row r="120" ht="19.5" customHeight="true">
+      <c r="A120" s="10"/>
+      <c r="B120" s="10"/>
+      <c r="C120" s="10"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120"/>
+      <c r="K120"/>
+      <c r="L120"/>
+      <c r="M120"/>
+      <c r="N120"/>
+      <c r="O120"/>
+      <c r="P120"/>
+      <c r="Q120"/>
+      <c r="R120"/>
+      <c r="S120"/>
+      <c r="T120"/>
+    </row>
+    <row r="121" ht="19.5" customHeight="true">
+      <c r="A121" s="10"/>
+      <c r="B121" s="10"/>
+      <c r="C121" s="10"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121"/>
+      <c r="K121"/>
+      <c r="L121"/>
+      <c r="M121"/>
+      <c r="N121"/>
+      <c r="O121"/>
+      <c r="P121"/>
+      <c r="Q121"/>
+      <c r="R121"/>
+      <c r="S121"/>
+      <c r="T121"/>
+    </row>
+    <row r="122" ht="19.5" customHeight="true">
+      <c r="A122" s="10"/>
+      <c r="B122" s="10"/>
+      <c r="C122" s="10"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
+      <c r="L122"/>
+      <c r="M122"/>
+      <c r="N122"/>
+      <c r="O122"/>
+      <c r="P122"/>
+      <c r="Q122"/>
+      <c r="R122"/>
+      <c r="S122"/>
+      <c r="T122"/>
+    </row>
+    <row r="123" ht="19.5" customHeight="true">
+      <c r="A123" s="10"/>
+      <c r="B123" s="10"/>
+      <c r="C123" s="10"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123"/>
+      <c r="I123"/>
+      <c r="J123"/>
+      <c r="K123"/>
+      <c r="L123"/>
+      <c r="M123"/>
+      <c r="N123"/>
+      <c r="O123"/>
+      <c r="P123"/>
+      <c r="Q123"/>
+      <c r="R123"/>
+      <c r="S123"/>
+      <c r="T123"/>
+    </row>
+    <row r="124" ht="19.5" customHeight="true">
+      <c r="A124" s="10"/>
+      <c r="B124" s="10"/>
+      <c r="C124" s="10"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="H124"/>
+      <c r="I124"/>
+      <c r="J124"/>
+      <c r="K124"/>
+      <c r="L124"/>
+      <c r="M124"/>
+      <c r="N124"/>
+      <c r="O124"/>
+      <c r="P124"/>
+      <c r="Q124"/>
+      <c r="R124"/>
+      <c r="S124"/>
+      <c r="T124"/>
+    </row>
+    <row r="125" ht="19.5" customHeight="true">
+      <c r="A125" s="10"/>
+      <c r="B125" s="10"/>
+      <c r="C125" s="10"/>
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="H125"/>
+      <c r="I125"/>
+      <c r="J125"/>
+      <c r="K125"/>
+      <c r="L125"/>
+      <c r="M125"/>
+      <c r="N125"/>
+      <c r="O125"/>
+      <c r="P125"/>
+      <c r="Q125"/>
+      <c r="R125"/>
+      <c r="S125"/>
+      <c r="T125"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="true">
+      <c r="A126" s="10"/>
+      <c r="B126" s="10"/>
+      <c r="C126" s="10"/>
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="H126"/>
+      <c r="I126"/>
+      <c r="J126"/>
+      <c r="K126"/>
+      <c r="L126"/>
+      <c r="M126"/>
+      <c r="N126"/>
+      <c r="O126"/>
+      <c r="P126"/>
+      <c r="Q126"/>
+      <c r="R126"/>
+      <c r="S126"/>
+      <c r="T126"/>
+    </row>
+    <row r="127" ht="19.5" customHeight="true">
+      <c r="A127" s="10"/>
+      <c r="B127" s="10"/>
+      <c r="C127" s="10"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="H127"/>
+      <c r="I127"/>
+      <c r="J127"/>
+      <c r="K127"/>
+      <c r="L127"/>
+      <c r="M127"/>
+      <c r="N127"/>
+      <c r="O127"/>
+      <c r="P127"/>
+      <c r="Q127"/>
+      <c r="R127"/>
+      <c r="S127"/>
+      <c r="T127"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="true">
+      <c r="A128" s="10"/>
+      <c r="B128" s="10"/>
+      <c r="C128" s="10"/>
+      <c r="D128"/>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="H128"/>
+      <c r="I128"/>
+      <c r="J128"/>
+      <c r="K128"/>
+      <c r="L128"/>
+      <c r="M128"/>
+      <c r="N128"/>
+      <c r="O128"/>
+      <c r="P128"/>
+      <c r="Q128"/>
+      <c r="R128"/>
+      <c r="S128"/>
+      <c r="T128"/>
+    </row>
+    <row r="129" ht="19.5" customHeight="true">
+      <c r="A129" s="10"/>
+      <c r="B129" s="10"/>
+      <c r="C129" s="10"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="I129"/>
+      <c r="J129"/>
+      <c r="K129"/>
+      <c r="L129"/>
+      <c r="M129"/>
+      <c r="N129"/>
+      <c r="O129"/>
+      <c r="P129"/>
+      <c r="Q129"/>
+      <c r="R129"/>
+      <c r="S129"/>
+      <c r="T129"/>
+    </row>
+    <row r="130" ht="19.5" customHeight="true">
+      <c r="A130" s="10"/>
+      <c r="B130" s="10"/>
+      <c r="C130" s="10"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
+      <c r="K130"/>
+      <c r="L130"/>
+      <c r="M130"/>
+      <c r="N130"/>
+      <c r="O130"/>
+      <c r="P130"/>
+      <c r="Q130"/>
+      <c r="R130"/>
+      <c r="S130"/>
+      <c r="T130"/>
+    </row>
+    <row r="131" ht="19.5" customHeight="true">
+      <c r="A131" s="10"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="10"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+      <c r="J131"/>
+      <c r="K131"/>
+      <c r="L131"/>
+      <c r="M131"/>
+      <c r="N131"/>
+      <c r="O131"/>
+      <c r="P131"/>
+      <c r="Q131"/>
+      <c r="R131"/>
+      <c r="S131"/>
+      <c r="T131"/>
+    </row>
+    <row r="132" ht="19.5" customHeight="true">
+      <c r="A132" s="10"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="10"/>
+      <c r="D132"/>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="H132"/>
+      <c r="I132"/>
+      <c r="J132"/>
+      <c r="K132"/>
+      <c r="L132"/>
+      <c r="M132"/>
+      <c r="N132"/>
+      <c r="O132"/>
+      <c r="P132"/>
+      <c r="Q132"/>
+      <c r="R132"/>
+      <c r="S132"/>
+      <c r="T132"/>
+    </row>
+    <row r="133" ht="19.5" customHeight="true">
+      <c r="A133" s="10"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="10"/>
+      <c r="D133"/>
+      <c r="E133"/>
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="H133"/>
+      <c r="I133"/>
+      <c r="J133"/>
+      <c r="K133"/>
+      <c r="L133"/>
+      <c r="M133"/>
+      <c r="N133"/>
+      <c r="O133"/>
+      <c r="P133"/>
+      <c r="Q133"/>
+      <c r="R133"/>
+      <c r="S133"/>
+      <c r="T133"/>
+    </row>
+    <row r="134" ht="19.5" customHeight="true">
+      <c r="A134" s="10"/>
+      <c r="B134" s="10"/>
+      <c r="C134" s="10"/>
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
+      <c r="G134"/>
+      <c r="H134"/>
+      <c r="I134"/>
+      <c r="J134"/>
+      <c r="K134"/>
+      <c r="L134"/>
+      <c r="M134"/>
+      <c r="N134"/>
+      <c r="O134"/>
+      <c r="P134"/>
+      <c r="Q134"/>
+      <c r="R134"/>
+      <c r="S134"/>
+      <c r="T134"/>
+    </row>
+    <row r="135" ht="19.5" customHeight="true">
+      <c r="A135" s="10"/>
+      <c r="B135" s="10"/>
+      <c r="C135" s="10"/>
+      <c r="D135"/>
+      <c r="E135"/>
+      <c r="F135"/>
+      <c r="G135"/>
+      <c r="H135"/>
+      <c r="I135"/>
+      <c r="J135"/>
+      <c r="K135"/>
+      <c r="L135"/>
+      <c r="M135"/>
+      <c r="N135"/>
+      <c r="O135"/>
+      <c r="P135"/>
+      <c r="Q135"/>
+      <c r="R135"/>
+      <c r="S135"/>
+      <c r="T135"/>
+    </row>
+    <row r="136" ht="19.5" customHeight="true">
+      <c r="A136" s="10"/>
+      <c r="B136" s="10"/>
+      <c r="C136" s="10"/>
+      <c r="D136"/>
+      <c r="E136"/>
+      <c r="F136"/>
+      <c r="G136"/>
+      <c r="H136"/>
+      <c r="I136"/>
+      <c r="J136"/>
+      <c r="K136"/>
+      <c r="L136"/>
+      <c r="M136"/>
+      <c r="N136"/>
+      <c r="O136"/>
+      <c r="P136"/>
+      <c r="Q136"/>
+      <c r="R136"/>
+      <c r="S136"/>
+      <c r="T136"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="true">
+      <c r="A137" s="10"/>
+      <c r="B137" s="10"/>
+      <c r="C137" s="10"/>
+      <c r="D137"/>
+      <c r="E137"/>
+      <c r="F137"/>
+      <c r="G137"/>
+      <c r="H137"/>
+      <c r="I137"/>
+      <c r="J137"/>
+      <c r="K137"/>
+      <c r="L137"/>
+      <c r="M137"/>
+      <c r="N137"/>
+      <c r="O137"/>
+      <c r="P137"/>
+      <c r="Q137"/>
+      <c r="R137"/>
+      <c r="S137"/>
+      <c r="T137"/>
+    </row>
+    <row r="138" ht="19.5" customHeight="true">
+      <c r="A138" s="10"/>
+      <c r="B138" s="10"/>
+      <c r="C138" s="10"/>
+      <c r="D138"/>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138"/>
+      <c r="I138"/>
+      <c r="J138"/>
+      <c r="K138"/>
+      <c r="L138"/>
+      <c r="M138"/>
+      <c r="N138"/>
+      <c r="O138"/>
+      <c r="P138"/>
+      <c r="Q138"/>
+      <c r="R138"/>
+      <c r="S138"/>
+      <c r="T138"/>
+    </row>
+    <row r="139" ht="19.5" customHeight="true">
+      <c r="A139" s="10"/>
+      <c r="B139" s="10"/>
+      <c r="C139" s="10"/>
+      <c r="D139"/>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="H139"/>
+      <c r="I139"/>
+      <c r="J139"/>
+      <c r="K139"/>
+      <c r="L139"/>
+      <c r="M139"/>
+      <c r="N139"/>
+      <c r="O139"/>
+      <c r="P139"/>
+      <c r="Q139"/>
+      <c r="R139"/>
+      <c r="S139"/>
+      <c r="T139"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="true">
+      <c r="A140" s="10"/>
+      <c r="B140" s="10"/>
+      <c r="C140" s="10"/>
+      <c r="D140"/>
+      <c r="E140"/>
+      <c r="F140"/>
+      <c r="G140"/>
+      <c r="H140"/>
+      <c r="I140"/>
+      <c r="J140"/>
+      <c r="K140"/>
+      <c r="L140"/>
+      <c r="M140"/>
+      <c r="N140"/>
+      <c r="O140"/>
+      <c r="P140"/>
+      <c r="Q140"/>
+      <c r="R140"/>
+      <c r="S140"/>
+      <c r="T140"/>
+    </row>
+    <row r="141" ht="19.5" customHeight="true">
+      <c r="A141" s="10"/>
+      <c r="B141" s="10"/>
+      <c r="C141" s="10"/>
+      <c r="D141"/>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141"/>
+      <c r="H141"/>
+      <c r="I141"/>
+      <c r="J141"/>
+      <c r="K141"/>
+      <c r="L141"/>
+      <c r="M141"/>
+      <c r="N141"/>
+      <c r="O141"/>
+      <c r="P141"/>
+      <c r="Q141"/>
+      <c r="R141"/>
+      <c r="S141"/>
+      <c r="T141"/>
+    </row>
+    <row r="142" ht="19.5" customHeight="true">
+      <c r="A142" s="10"/>
+      <c r="B142" s="10"/>
+      <c r="C142" s="10"/>
+      <c r="D142"/>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142"/>
+      <c r="H142"/>
+      <c r="I142"/>
+      <c r="J142"/>
+      <c r="K142"/>
+      <c r="L142"/>
+      <c r="M142"/>
+      <c r="N142"/>
+      <c r="O142"/>
+      <c r="P142"/>
+      <c r="Q142"/>
+      <c r="R142"/>
+      <c r="S142"/>
+      <c r="T142"/>
+    </row>
+    <row r="143" ht="19.5" customHeight="true">
+      <c r="A143" s="10"/>
+      <c r="B143" s="10"/>
+      <c r="C143" s="10"/>
+      <c r="D143"/>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143"/>
+      <c r="H143"/>
+      <c r="I143"/>
+      <c r="J143"/>
+      <c r="K143"/>
+      <c r="L143"/>
+      <c r="M143"/>
+      <c r="N143"/>
+      <c r="O143"/>
+      <c r="P143"/>
+      <c r="Q143"/>
+      <c r="R143"/>
+      <c r="S143"/>
+      <c r="T143"/>
+    </row>
+    <row r="144" ht="19.5" customHeight="true">
+      <c r="A144" s="10"/>
+      <c r="B144" s="10"/>
+      <c r="C144" s="10"/>
+      <c r="D144"/>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="H144"/>
+      <c r="I144"/>
+      <c r="J144"/>
+      <c r="K144"/>
+      <c r="L144"/>
+      <c r="M144"/>
+      <c r="N144"/>
+      <c r="O144"/>
+      <c r="P144"/>
+      <c r="Q144"/>
+      <c r="R144"/>
+      <c r="S144"/>
+      <c r="T144"/>
+    </row>
+    <row r="145" ht="19.5" customHeight="true">
+      <c r="A145" s="10"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="H145"/>
+      <c r="I145"/>
+      <c r="J145"/>
+      <c r="K145"/>
+      <c r="L145"/>
+      <c r="M145"/>
+      <c r="N145"/>
+      <c r="O145"/>
+      <c r="P145"/>
+      <c r="Q145"/>
+      <c r="R145"/>
+      <c r="S145"/>
+      <c r="T145"/>
+    </row>
+    <row r="146" ht="19.5" customHeight="true">
+      <c r="A146" s="10"/>
+      <c r="B146" s="10"/>
+      <c r="C146" s="10"/>
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="H146"/>
+      <c r="I146"/>
+      <c r="J146"/>
+      <c r="K146"/>
+      <c r="L146"/>
+      <c r="M146"/>
+      <c r="N146"/>
+      <c r="O146"/>
+      <c r="P146"/>
+      <c r="Q146"/>
+      <c r="R146"/>
+      <c r="S146"/>
+      <c r="T146"/>
+    </row>
+    <row r="147" ht="19.5" customHeight="true">
+      <c r="A147" s="10"/>
+      <c r="B147" s="10"/>
+      <c r="C147" s="10"/>
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147"/>
+      <c r="H147"/>
+      <c r="I147"/>
+      <c r="J147"/>
+      <c r="K147"/>
+      <c r="L147"/>
+      <c r="M147"/>
+      <c r="N147"/>
+      <c r="O147"/>
+      <c r="P147"/>
+      <c r="Q147"/>
+      <c r="R147"/>
+      <c r="S147"/>
+      <c r="T147"/>
+    </row>
+    <row r="148" ht="19.5" customHeight="true">
+      <c r="A148" s="10"/>
+      <c r="B148" s="10"/>
+      <c r="C148" s="10"/>
+      <c r="D148"/>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148"/>
+      <c r="H148"/>
+      <c r="I148"/>
+      <c r="J148"/>
+      <c r="K148"/>
+      <c r="L148"/>
+      <c r="M148"/>
+      <c r="N148"/>
+      <c r="O148"/>
+      <c r="P148"/>
+      <c r="Q148"/>
+      <c r="R148"/>
+      <c r="S148"/>
+      <c r="T148"/>
+    </row>
+    <row r="149" ht="19.5" customHeight="true">
+      <c r="A149" s="10"/>
+      <c r="B149" s="10"/>
+      <c r="C149" s="10"/>
+      <c r="D149"/>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149"/>
+      <c r="H149"/>
+      <c r="I149"/>
+      <c r="J149"/>
+      <c r="K149"/>
+      <c r="L149"/>
+      <c r="M149"/>
+      <c r="N149"/>
+      <c r="O149"/>
+      <c r="P149"/>
+      <c r="Q149"/>
+      <c r="R149"/>
+      <c r="S149"/>
+      <c r="T149"/>
+    </row>
+    <row r="150" ht="19.5" customHeight="true">
+      <c r="A150" s="10"/>
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
+      <c r="D150"/>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150"/>
+      <c r="H150"/>
+      <c r="I150"/>
+      <c r="J150"/>
+      <c r="K150"/>
+      <c r="L150"/>
+      <c r="M150"/>
+      <c r="N150"/>
+      <c r="O150"/>
+      <c r="P150"/>
+      <c r="Q150"/>
+      <c r="R150"/>
+      <c r="S150"/>
+      <c r="T150"/>
+    </row>
+    <row r="151" ht="19.5" customHeight="true">
+      <c r="A151" s="10"/>
+      <c r="B151" s="10"/>
+      <c r="C151" s="10"/>
+      <c r="D151"/>
+      <c r="E151"/>
+      <c r="F151"/>
+      <c r="G151"/>
+      <c r="H151"/>
+      <c r="I151"/>
+      <c r="J151"/>
+      <c r="K151"/>
+      <c r="L151"/>
+      <c r="M151"/>
+      <c r="N151"/>
+      <c r="O151"/>
+      <c r="P151"/>
+      <c r="Q151"/>
+      <c r="R151"/>
+      <c r="S151"/>
+      <c r="T151"/>
+    </row>
+    <row r="152" ht="19.5" customHeight="true">
+      <c r="A152" s="10"/>
+      <c r="B152" s="10"/>
+      <c r="C152" s="10"/>
+      <c r="D152"/>
+      <c r="E152"/>
+      <c r="F152"/>
+      <c r="G152"/>
+      <c r="H152"/>
+      <c r="I152"/>
+      <c r="J152"/>
+      <c r="K152"/>
+      <c r="L152"/>
+      <c r="M152"/>
+      <c r="N152"/>
+      <c r="O152"/>
+      <c r="P152"/>
+      <c r="Q152"/>
+      <c r="R152"/>
+      <c r="S152"/>
+      <c r="T152"/>
+    </row>
+    <row r="153" ht="19.5" customHeight="true">
+      <c r="A153" s="10"/>
+      <c r="B153" s="10"/>
+      <c r="C153" s="10"/>
+      <c r="D153"/>
+      <c r="E153"/>
+      <c r="F153"/>
+      <c r="G153"/>
+      <c r="H153"/>
+      <c r="I153"/>
+      <c r="J153"/>
+      <c r="K153"/>
+      <c r="L153"/>
+      <c r="M153"/>
+      <c r="N153"/>
+      <c r="O153"/>
+      <c r="P153"/>
+      <c r="Q153"/>
+      <c r="R153"/>
+      <c r="S153"/>
+      <c r="T153"/>
+    </row>
+    <row r="154" ht="19.5" customHeight="true">
+      <c r="A154" s="10"/>
+      <c r="B154" s="10"/>
+      <c r="C154" s="10"/>
+      <c r="D154"/>
+      <c r="E154"/>
+      <c r="F154"/>
+      <c r="G154"/>
+      <c r="H154"/>
+      <c r="I154"/>
+      <c r="J154"/>
+      <c r="K154"/>
+      <c r="L154"/>
+      <c r="M154"/>
+      <c r="N154"/>
+      <c r="O154"/>
+      <c r="P154"/>
+      <c r="Q154"/>
+      <c r="R154"/>
+      <c r="S154"/>
+      <c r="T154"/>
+    </row>
+    <row r="155" ht="19.5" customHeight="true">
+      <c r="A155" s="10"/>
+      <c r="B155" s="10"/>
+      <c r="C155" s="10"/>
+      <c r="D155"/>
+      <c r="E155"/>
+      <c r="F155"/>
+      <c r="G155"/>
+      <c r="H155"/>
+      <c r="I155"/>
+      <c r="J155"/>
+      <c r="K155"/>
+      <c r="L155"/>
+      <c r="M155"/>
+      <c r="N155"/>
+      <c r="O155"/>
+      <c r="P155"/>
+      <c r="Q155"/>
+      <c r="R155"/>
+      <c r="S155"/>
+      <c r="T155"/>
+    </row>
+    <row r="156" ht="19.5" customHeight="true">
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
+      <c r="C156" s="10"/>
+      <c r="D156"/>
+      <c r="E156"/>
+      <c r="F156"/>
+      <c r="G156"/>
+      <c r="H156"/>
+      <c r="I156"/>
+      <c r="J156"/>
+      <c r="K156"/>
+      <c r="L156"/>
+      <c r="M156"/>
+      <c r="N156"/>
+      <c r="O156"/>
+      <c r="P156"/>
+      <c r="Q156"/>
+      <c r="R156"/>
+      <c r="S156"/>
+      <c r="T156"/>
+    </row>
+    <row r="157" ht="19.5" customHeight="true">
+      <c r="A157" s="10"/>
+      <c r="B157" s="10"/>
+      <c r="C157" s="10"/>
+      <c r="D157"/>
+      <c r="E157"/>
+      <c r="F157"/>
+      <c r="G157"/>
+      <c r="H157"/>
+      <c r="I157"/>
+      <c r="J157"/>
+      <c r="K157"/>
+      <c r="L157"/>
+      <c r="M157"/>
+      <c r="N157"/>
+      <c r="O157"/>
+      <c r="P157"/>
+      <c r="Q157"/>
+      <c r="R157"/>
+      <c r="S157"/>
+      <c r="T157"/>
+    </row>
+    <row r="158" ht="19.5" customHeight="true">
+      <c r="A158" s="10"/>
+      <c r="B158" s="10"/>
+      <c r="C158" s="10"/>
+      <c r="D158"/>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158"/>
+      <c r="H158"/>
+      <c r="I158"/>
+      <c r="J158"/>
+      <c r="K158"/>
+      <c r="L158"/>
+      <c r="M158"/>
+      <c r="N158"/>
+      <c r="O158"/>
+      <c r="P158"/>
+      <c r="Q158"/>
+      <c r="R158"/>
+      <c r="S158"/>
+      <c r="T158"/>
+    </row>
+    <row r="159" ht="19.5" customHeight="true">
+      <c r="A159" s="10"/>
+      <c r="B159" s="10"/>
+      <c r="C159" s="10"/>
+      <c r="D159"/>
+      <c r="E159"/>
+      <c r="F159"/>
+      <c r="G159"/>
+      <c r="H159"/>
+      <c r="I159"/>
+      <c r="J159"/>
+      <c r="K159"/>
+      <c r="L159"/>
+      <c r="M159"/>
+      <c r="N159"/>
+      <c r="O159"/>
+      <c r="P159"/>
+      <c r="Q159"/>
+      <c r="R159"/>
+      <c r="S159"/>
+      <c r="T159"/>
+    </row>
+    <row r="160" ht="19.5" customHeight="true">
+      <c r="A160" s="10"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
+      <c r="D160"/>
+      <c r="E160"/>
+      <c r="F160"/>
+      <c r="G160"/>
+      <c r="H160"/>
+      <c r="I160"/>
+      <c r="J160"/>
+      <c r="K160"/>
+      <c r="L160"/>
+      <c r="M160"/>
+      <c r="N160"/>
+      <c r="O160"/>
+      <c r="P160"/>
+      <c r="Q160"/>
+      <c r="R160"/>
+      <c r="S160"/>
+      <c r="T160"/>
+    </row>
+    <row r="161" ht="19.5" customHeight="true">
+      <c r="A161" s="10"/>
+      <c r="B161" s="10"/>
+      <c r="C161" s="10"/>
+      <c r="D161"/>
+      <c r="E161"/>
+      <c r="F161"/>
+      <c r="G161"/>
+      <c r="H161"/>
+      <c r="I161"/>
+      <c r="J161"/>
+      <c r="K161"/>
+      <c r="L161"/>
+      <c r="M161"/>
+      <c r="N161"/>
+      <c r="O161"/>
+      <c r="P161"/>
+      <c r="Q161"/>
+      <c r="R161"/>
+      <c r="S161"/>
+      <c r="T161"/>
+    </row>
+    <row r="162" ht="19.5" customHeight="true">
+      <c r="A162" s="10"/>
+      <c r="B162" s="10"/>
+      <c r="C162" s="10"/>
+      <c r="D162"/>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162"/>
+      <c r="H162"/>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="K162"/>
+      <c r="L162"/>
+      <c r="M162"/>
+      <c r="N162"/>
+      <c r="O162"/>
+      <c r="P162"/>
+      <c r="Q162"/>
+      <c r="R162"/>
+      <c r="S162"/>
+      <c r="T162"/>
+    </row>
+    <row r="163" ht="19.5" customHeight="true">
+      <c r="A163" s="10"/>
+      <c r="B163" s="10"/>
+      <c r="C163" s="10"/>
+      <c r="D163"/>
+      <c r="E163"/>
+      <c r="F163"/>
+      <c r="G163"/>
+      <c r="H163"/>
+      <c r="I163"/>
+      <c r="J163"/>
+      <c r="K163"/>
+      <c r="L163"/>
+      <c r="M163"/>
+      <c r="N163"/>
+      <c r="O163"/>
+      <c r="P163"/>
+      <c r="Q163"/>
+      <c r="R163"/>
+      <c r="S163"/>
+      <c r="T163"/>
+    </row>
+    <row r="164" ht="19.5" customHeight="true">
+      <c r="A164" s="10"/>
+      <c r="B164" s="10"/>
+      <c r="C164" s="10"/>
+      <c r="D164"/>
+      <c r="E164"/>
+      <c r="F164"/>
+      <c r="G164"/>
+      <c r="H164"/>
+      <c r="I164"/>
+      <c r="J164"/>
+      <c r="K164"/>
+      <c r="L164"/>
+      <c r="M164"/>
+      <c r="N164"/>
+      <c r="O164"/>
+      <c r="P164"/>
+      <c r="Q164"/>
+      <c r="R164"/>
+      <c r="S164"/>
+      <c r="T164"/>
+    </row>
+    <row r="165" ht="19.5" customHeight="true">
+      <c r="A165" s="10"/>
+      <c r="B165" s="10"/>
+      <c r="C165" s="10"/>
+      <c r="D165"/>
+      <c r="E165"/>
+      <c r="F165"/>
+      <c r="G165"/>
+      <c r="H165"/>
+      <c r="I165"/>
+      <c r="J165"/>
+      <c r="K165"/>
+      <c r="L165"/>
+      <c r="M165"/>
+      <c r="N165"/>
+      <c r="O165"/>
+      <c r="P165"/>
+      <c r="Q165"/>
+      <c r="R165"/>
+      <c r="S165"/>
+      <c r="T165"/>
+    </row>
+    <row r="166" ht="19.5" customHeight="true">
+      <c r="A166" s="10"/>
+      <c r="B166" s="10"/>
+      <c r="C166" s="10"/>
+      <c r="D166"/>
+      <c r="E166"/>
+      <c r="F166"/>
+      <c r="G166"/>
+      <c r="H166"/>
+      <c r="I166"/>
+      <c r="J166"/>
+      <c r="K166"/>
+      <c r="L166"/>
+      <c r="M166"/>
+      <c r="N166"/>
+      <c r="O166"/>
+      <c r="P166"/>
+      <c r="Q166"/>
+      <c r="R166"/>
+      <c r="S166"/>
+      <c r="T166"/>
+    </row>
+    <row r="167" ht="19.5" customHeight="true">
+      <c r="A167" s="10"/>
+      <c r="B167" s="10"/>
+      <c r="C167" s="10"/>
+      <c r="D167"/>
+      <c r="E167"/>
+      <c r="F167"/>
+      <c r="G167"/>
+      <c r="H167"/>
+      <c r="I167"/>
+      <c r="J167"/>
+      <c r="K167"/>
+      <c r="L167"/>
+      <c r="M167"/>
+      <c r="N167"/>
+      <c r="O167"/>
+      <c r="P167"/>
+      <c r="Q167"/>
+      <c r="R167"/>
+      <c r="S167"/>
+      <c r="T167"/>
+    </row>
+    <row r="168" ht="19.5" customHeight="true">
+      <c r="A168" s="10"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="10"/>
+      <c r="D168"/>
+      <c r="E168"/>
+      <c r="F168"/>
+      <c r="G168"/>
+      <c r="H168"/>
+      <c r="I168"/>
+      <c r="J168"/>
+      <c r="K168"/>
+      <c r="L168"/>
+      <c r="M168"/>
+      <c r="N168"/>
+      <c r="O168"/>
+      <c r="P168"/>
+      <c r="Q168"/>
+      <c r="R168"/>
+      <c r="S168"/>
+      <c r="T168"/>
+    </row>
+    <row r="169" ht="19.5" customHeight="true">
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="10"/>
+      <c r="D169"/>
+      <c r="E169"/>
+      <c r="F169"/>
+      <c r="G169"/>
+      <c r="H169"/>
+      <c r="I169"/>
+      <c r="J169"/>
+      <c r="K169"/>
+      <c r="L169"/>
+      <c r="M169"/>
+      <c r="N169"/>
+      <c r="O169"/>
+      <c r="P169"/>
+      <c r="Q169"/>
+      <c r="R169"/>
+      <c r="S169"/>
+      <c r="T169"/>
+    </row>
+    <row r="170" ht="19.5" customHeight="true">
+      <c r="A170" s="10"/>
+      <c r="B170" s="10"/>
+      <c r="C170" s="10"/>
+      <c r="D170"/>
+      <c r="E170"/>
+      <c r="F170"/>
+      <c r="G170"/>
+      <c r="H170"/>
+      <c r="I170"/>
+      <c r="J170"/>
+      <c r="K170"/>
+      <c r="L170"/>
+      <c r="M170"/>
+      <c r="N170"/>
+      <c r="O170"/>
+      <c r="P170"/>
+      <c r="Q170"/>
+      <c r="R170"/>
+      <c r="S170"/>
+      <c r="T170"/>
+    </row>
+    <row r="171" ht="19.5" customHeight="true">
+      <c r="A171" s="10"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="10"/>
+      <c r="D171"/>
+      <c r="E171"/>
+      <c r="F171"/>
+      <c r="G171"/>
+      <c r="H171"/>
+      <c r="I171"/>
+      <c r="J171"/>
+      <c r="K171"/>
+      <c r="L171"/>
+      <c r="M171"/>
+      <c r="N171"/>
+      <c r="O171"/>
+      <c r="P171"/>
+      <c r="Q171"/>
+      <c r="R171"/>
+      <c r="S171"/>
+      <c r="T171"/>
+    </row>
+    <row r="172" ht="19.5" customHeight="true">
+      <c r="A172" s="10"/>
+      <c r="B172" s="10"/>
+      <c r="C172" s="10"/>
+      <c r="D172"/>
+      <c r="E172"/>
+      <c r="F172"/>
+      <c r="G172"/>
+      <c r="H172"/>
+      <c r="I172"/>
+      <c r="J172"/>
+      <c r="K172"/>
+      <c r="L172"/>
+      <c r="M172"/>
+      <c r="N172"/>
+      <c r="O172"/>
+      <c r="P172"/>
+      <c r="Q172"/>
+      <c r="R172"/>
+      <c r="S172"/>
+      <c r="T172"/>
+    </row>
+    <row r="173" ht="19.5" customHeight="true">
+      <c r="A173" s="10"/>
+      <c r="B173" s="10"/>
+      <c r="C173" s="10"/>
+      <c r="D173"/>
+      <c r="E173"/>
+      <c r="F173"/>
+      <c r="G173"/>
+      <c r="H173"/>
+      <c r="I173"/>
+      <c r="J173"/>
+      <c r="K173"/>
+      <c r="L173"/>
+      <c r="M173"/>
+      <c r="N173"/>
+      <c r="O173"/>
+      <c r="P173"/>
+      <c r="Q173"/>
+      <c r="R173"/>
+      <c r="S173"/>
+      <c r="T173"/>
+    </row>
+    <row r="174" ht="19.5" customHeight="true">
+      <c r="A174" s="10"/>
+      <c r="B174" s="10"/>
+      <c r="C174" s="10"/>
+      <c r="D174"/>
+      <c r="E174"/>
+      <c r="F174"/>
+      <c r="G174"/>
+      <c r="H174"/>
+      <c r="I174"/>
+      <c r="J174"/>
+      <c r="K174"/>
+      <c r="L174"/>
+      <c r="M174"/>
+      <c r="N174"/>
+      <c r="O174"/>
+      <c r="P174"/>
+      <c r="Q174"/>
+      <c r="R174"/>
+      <c r="S174"/>
+      <c r="T174"/>
+    </row>
+    <row r="175" ht="19.5" customHeight="true">
+      <c r="A175" s="10"/>
+      <c r="B175" s="10"/>
+      <c r="C175" s="10"/>
+      <c r="D175"/>
+      <c r="E175"/>
+      <c r="F175"/>
+      <c r="G175"/>
+      <c r="H175"/>
+      <c r="I175"/>
+      <c r="J175"/>
+      <c r="K175"/>
+      <c r="L175"/>
+      <c r="M175"/>
+      <c r="N175"/>
+      <c r="O175"/>
+      <c r="P175"/>
+      <c r="Q175"/>
+      <c r="R175"/>
+      <c r="S175"/>
+      <c r="T175"/>
+    </row>
+    <row r="176" ht="19.5" customHeight="true">
+      <c r="A176" s="10"/>
+      <c r="B176" s="10"/>
+      <c r="C176" s="10"/>
+      <c r="D176"/>
+      <c r="E176"/>
+      <c r="F176"/>
+      <c r="G176"/>
+      <c r="H176"/>
+      <c r="I176"/>
+      <c r="J176"/>
+      <c r="K176"/>
+      <c r="L176"/>
+      <c r="M176"/>
+      <c r="N176"/>
+      <c r="O176"/>
+      <c r="P176"/>
+      <c r="Q176"/>
+      <c r="R176"/>
+      <c r="S176"/>
+      <c r="T176"/>
+    </row>
+    <row r="177" ht="19.5" customHeight="true">
+      <c r="A177" s="10"/>
+      <c r="B177" s="10"/>
+      <c r="C177" s="10"/>
+      <c r="D177"/>
+      <c r="E177"/>
+      <c r="F177"/>
+      <c r="G177"/>
+      <c r="H177"/>
+      <c r="I177"/>
+      <c r="J177"/>
+      <c r="K177"/>
+      <c r="L177"/>
+      <c r="M177"/>
+      <c r="N177"/>
+      <c r="O177"/>
+      <c r="P177"/>
+      <c r="Q177"/>
+      <c r="R177"/>
+      <c r="S177"/>
+      <c r="T177"/>
+    </row>
+    <row r="178" ht="19.5" customHeight="true">
+      <c r="A178" s="10"/>
+      <c r="B178" s="10"/>
+      <c r="C178" s="10"/>
+      <c r="D178"/>
+      <c r="E178"/>
+      <c r="F178"/>
+      <c r="G178"/>
+      <c r="H178"/>
+      <c r="I178"/>
+      <c r="J178"/>
+      <c r="K178"/>
+      <c r="L178"/>
+      <c r="M178"/>
+      <c r="N178"/>
+      <c r="O178"/>
+      <c r="P178"/>
+      <c r="Q178"/>
+      <c r="R178"/>
+      <c r="S178"/>
+      <c r="T178"/>
+    </row>
+    <row r="179" ht="19.5" customHeight="true">
+      <c r="A179" s="10"/>
+      <c r="B179" s="10"/>
+      <c r="C179" s="10"/>
+      <c r="D179"/>
+      <c r="E179"/>
+      <c r="F179"/>
+      <c r="G179"/>
+      <c r="H179"/>
+      <c r="I179"/>
+      <c r="J179"/>
+      <c r="K179"/>
+      <c r="L179"/>
+      <c r="M179"/>
+      <c r="N179"/>
+      <c r="O179"/>
+      <c r="P179"/>
+      <c r="Q179"/>
+      <c r="R179"/>
+      <c r="S179"/>
+      <c r="T179"/>
+    </row>
+    <row r="180" ht="19.5" customHeight="true">
+      <c r="A180" s="10"/>
+      <c r="B180" s="10"/>
+      <c r="C180" s="10"/>
+      <c r="D180"/>
+      <c r="E180"/>
+      <c r="F180"/>
+      <c r="G180"/>
+      <c r="H180"/>
+      <c r="I180"/>
+      <c r="J180"/>
+      <c r="K180"/>
+      <c r="L180"/>
+      <c r="M180"/>
+      <c r="N180"/>
+      <c r="O180"/>
+      <c r="P180"/>
+      <c r="Q180"/>
+      <c r="R180"/>
+      <c r="S180"/>
+      <c r="T180"/>
+    </row>
+    <row r="181" ht="19.5" customHeight="true">
+      <c r="A181" s="10"/>
+      <c r="B181" s="10"/>
+      <c r="C181" s="10"/>
+      <c r="D181"/>
+      <c r="E181"/>
+      <c r="F181"/>
+      <c r="G181"/>
+      <c r="H181"/>
+      <c r="I181"/>
+      <c r="J181"/>
+      <c r="K181"/>
+      <c r="L181"/>
+      <c r="M181"/>
+      <c r="N181"/>
+      <c r="O181"/>
+      <c r="P181"/>
+      <c r="Q181"/>
+      <c r="R181"/>
+      <c r="S181"/>
+      <c r="T181"/>
+    </row>
+    <row r="182" ht="19.5" customHeight="true">
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
+      <c r="C182" s="10"/>
+      <c r="D182"/>
+      <c r="E182"/>
+      <c r="F182"/>
+      <c r="G182"/>
+      <c r="H182"/>
+      <c r="I182"/>
+      <c r="J182"/>
+      <c r="K182"/>
+      <c r="L182"/>
+      <c r="M182"/>
+      <c r="N182"/>
+      <c r="O182"/>
+      <c r="P182"/>
+      <c r="Q182"/>
+      <c r="R182"/>
+      <c r="S182"/>
+      <c r="T182"/>
+    </row>
+    <row r="183" ht="19.5" customHeight="true">
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
+      <c r="C183" s="10"/>
+      <c r="D183"/>
+      <c r="E183"/>
+      <c r="F183"/>
+      <c r="G183"/>
+      <c r="H183"/>
+      <c r="I183"/>
+      <c r="J183"/>
+      <c r="K183"/>
+      <c r="L183"/>
+      <c r="M183"/>
+      <c r="N183"/>
+      <c r="O183"/>
+      <c r="P183"/>
+      <c r="Q183"/>
+      <c r="R183"/>
+      <c r="S183"/>
+      <c r="T183"/>
+    </row>
+    <row r="184" ht="19.5" customHeight="true">
+      <c r="A184" s="10"/>
+      <c r="B184" s="10"/>
+      <c r="C184" s="10"/>
+      <c r="D184"/>
+      <c r="E184"/>
+      <c r="F184"/>
+      <c r="G184"/>
+      <c r="H184"/>
+      <c r="I184"/>
+      <c r="J184"/>
+      <c r="K184"/>
+      <c r="L184"/>
+      <c r="M184"/>
+      <c r="N184"/>
+      <c r="O184"/>
+      <c r="P184"/>
+      <c r="Q184"/>
+      <c r="R184"/>
+      <c r="S184"/>
+      <c r="T184"/>
+    </row>
+    <row r="185" ht="19.5" customHeight="true">
+      <c r="A185" s="10"/>
+      <c r="B185" s="10"/>
+      <c r="C185" s="10"/>
+      <c r="D185"/>
+      <c r="E185"/>
+      <c r="F185"/>
+      <c r="G185"/>
+      <c r="H185"/>
+      <c r="I185"/>
+      <c r="J185"/>
+      <c r="K185"/>
+      <c r="L185"/>
+      <c r="M185"/>
+      <c r="N185"/>
+      <c r="O185"/>
+      <c r="P185"/>
+      <c r="Q185"/>
+      <c r="R185"/>
+      <c r="S185"/>
+      <c r="T185"/>
+    </row>
+    <row r="186" ht="19.5" customHeight="true">
+      <c r="A186" s="10"/>
+      <c r="B186" s="10"/>
+      <c r="C186" s="10"/>
+      <c r="D186"/>
+      <c r="E186"/>
+      <c r="F186"/>
+      <c r="G186"/>
+      <c r="H186"/>
+      <c r="I186"/>
+      <c r="J186"/>
+      <c r="K186"/>
+      <c r="L186"/>
+      <c r="M186"/>
+      <c r="N186"/>
+      <c r="O186"/>
+      <c r="P186"/>
+      <c r="Q186"/>
+      <c r="R186"/>
+      <c r="S186"/>
+      <c r="T186"/>
+    </row>
+    <row r="187" ht="19.5" customHeight="true">
+      <c r="A187" s="10"/>
+      <c r="B187" s="10"/>
+      <c r="C187" s="10"/>
+      <c r="D187"/>
+      <c r="E187"/>
+      <c r="F187"/>
+      <c r="G187"/>
+      <c r="H187"/>
+      <c r="I187"/>
+      <c r="J187"/>
+      <c r="K187"/>
+      <c r="L187"/>
+      <c r="M187"/>
+      <c r="N187"/>
+      <c r="O187"/>
+      <c r="P187"/>
+      <c r="Q187"/>
+      <c r="R187"/>
+      <c r="S187"/>
+      <c r="T187"/>
+    </row>
+    <row r="188" ht="19.5" customHeight="true">
+      <c r="A188" s="10"/>
+      <c r="B188" s="10"/>
+      <c r="C188" s="10"/>
+      <c r="D188"/>
+      <c r="E188"/>
+      <c r="F188"/>
+      <c r="G188"/>
+      <c r="H188"/>
+      <c r="I188"/>
+      <c r="J188"/>
+      <c r="K188"/>
+      <c r="L188"/>
+      <c r="M188"/>
+      <c r="N188"/>
+      <c r="O188"/>
+      <c r="P188"/>
+      <c r="Q188"/>
+      <c r="R188"/>
+      <c r="S188"/>
+      <c r="T188"/>
+    </row>
+    <row r="189" ht="19.5" customHeight="true">
+      <c r="A189" s="10"/>
+      <c r="B189" s="10"/>
+      <c r="C189" s="10"/>
+      <c r="D189"/>
+      <c r="E189"/>
+      <c r="F189"/>
+      <c r="G189"/>
+      <c r="H189"/>
+      <c r="I189"/>
+      <c r="J189"/>
+      <c r="K189"/>
+      <c r="L189"/>
+      <c r="M189"/>
+      <c r="N189"/>
+      <c r="O189"/>
+      <c r="P189"/>
+      <c r="Q189"/>
+      <c r="R189"/>
+      <c r="S189"/>
+      <c r="T189"/>
+    </row>
+    <row r="190" ht="19.5" customHeight="true">
+      <c r="A190" s="10"/>
+      <c r="B190" s="10"/>
+      <c r="C190" s="10"/>
+      <c r="D190"/>
+      <c r="E190"/>
+      <c r="F190"/>
+      <c r="G190"/>
+      <c r="H190"/>
+      <c r="I190"/>
+      <c r="J190"/>
+      <c r="K190"/>
+      <c r="L190"/>
+      <c r="M190"/>
+      <c r="N190"/>
+      <c r="O190"/>
+      <c r="P190"/>
+      <c r="Q190"/>
+      <c r="R190"/>
+      <c r="S190"/>
+      <c r="T190"/>
+    </row>
+    <row r="191" ht="19.5" customHeight="true">
+      <c r="A191" s="10"/>
+      <c r="B191" s="10"/>
+      <c r="C191" s="10"/>
+      <c r="D191"/>
+      <c r="E191"/>
+      <c r="F191"/>
+      <c r="G191"/>
+      <c r="H191"/>
+      <c r="I191"/>
+      <c r="J191"/>
+      <c r="K191"/>
+      <c r="L191"/>
+      <c r="M191"/>
+      <c r="N191"/>
+      <c r="O191"/>
+      <c r="P191"/>
+      <c r="Q191"/>
+      <c r="R191"/>
+      <c r="S191"/>
+      <c r="T191"/>
+    </row>
+    <row r="192" ht="19.5" customHeight="true">
+      <c r="A192" s="10"/>
+      <c r="B192" s="10"/>
+      <c r="C192" s="10"/>
+      <c r="D192"/>
+      <c r="E192"/>
+      <c r="F192"/>
+      <c r="G192"/>
+      <c r="H192"/>
+      <c r="I192"/>
+      <c r="J192"/>
+      <c r="K192"/>
+      <c r="L192"/>
+      <c r="M192"/>
+      <c r="N192"/>
+      <c r="O192"/>
+      <c r="P192"/>
+      <c r="Q192"/>
+      <c r="R192"/>
+      <c r="S192"/>
+      <c r="T192"/>
+    </row>
+    <row r="193" ht="19.5" customHeight="true">
+      <c r="A193" s="10"/>
+      <c r="B193" s="10"/>
+      <c r="C193" s="10"/>
+      <c r="D193"/>
+      <c r="E193"/>
+      <c r="F193"/>
+      <c r="G193"/>
+      <c r="H193"/>
+      <c r="I193"/>
+      <c r="J193"/>
+      <c r="K193"/>
+      <c r="L193"/>
+      <c r="M193"/>
+      <c r="N193"/>
+      <c r="O193"/>
+      <c r="P193"/>
+      <c r="Q193"/>
+      <c r="R193"/>
+      <c r="S193"/>
+      <c r="T193"/>
+    </row>
+    <row r="194" ht="19.5" customHeight="true">
+      <c r="A194" s="10"/>
+      <c r="B194" s="10"/>
+      <c r="C194" s="10"/>
+      <c r="D194"/>
+      <c r="E194"/>
+      <c r="F194"/>
+      <c r="G194"/>
+      <c r="H194"/>
+      <c r="I194"/>
+      <c r="J194"/>
+      <c r="K194"/>
+      <c r="L194"/>
+      <c r="M194"/>
+      <c r="N194"/>
+      <c r="O194"/>
+      <c r="P194"/>
+      <c r="Q194"/>
+      <c r="R194"/>
+      <c r="S194"/>
+      <c r="T194"/>
+    </row>
+    <row r="195" ht="19.5" customHeight="true">
+      <c r="A195" s="10"/>
+      <c r="B195" s="10"/>
+      <c r="C195" s="10"/>
+      <c r="D195"/>
+      <c r="E195"/>
+      <c r="F195"/>
+      <c r="G195"/>
+      <c r="H195"/>
+      <c r="I195"/>
+      <c r="J195"/>
+      <c r="K195"/>
+      <c r="L195"/>
+      <c r="M195"/>
+      <c r="N195"/>
+      <c r="O195"/>
+      <c r="P195"/>
+      <c r="Q195"/>
+      <c r="R195"/>
+      <c r="S195"/>
+      <c r="T195"/>
+    </row>
+    <row r="196" ht="19.5" customHeight="true">
+      <c r="A196" s="10"/>
+      <c r="B196" s="10"/>
+      <c r="C196" s="10"/>
+      <c r="D196"/>
+      <c r="E196"/>
+      <c r="F196"/>
+      <c r="G196"/>
+      <c r="H196"/>
+      <c r="I196"/>
+      <c r="J196"/>
+      <c r="K196"/>
+      <c r="L196"/>
+      <c r="M196"/>
+      <c r="N196"/>
+      <c r="O196"/>
+      <c r="P196"/>
+      <c r="Q196"/>
+      <c r="R196"/>
+      <c r="S196"/>
+      <c r="T196"/>
+    </row>
+    <row r="197" ht="19.5" customHeight="true">
+      <c r="A197" s="10"/>
+      <c r="B197" s="10"/>
+      <c r="C197" s="10"/>
+      <c r="D197"/>
+      <c r="E197"/>
+      <c r="F197"/>
+      <c r="G197"/>
+      <c r="H197"/>
+      <c r="I197"/>
+      <c r="J197"/>
+      <c r="K197"/>
+      <c r="L197"/>
+      <c r="M197"/>
+      <c r="N197"/>
+      <c r="O197"/>
+      <c r="P197"/>
+      <c r="Q197"/>
+      <c r="R197"/>
+      <c r="S197"/>
+      <c r="T197"/>
+    </row>
+    <row r="198" ht="19.5" customHeight="true">
+      <c r="A198" s="10"/>
+      <c r="B198" s="10"/>
+      <c r="C198" s="10"/>
+      <c r="D198"/>
+      <c r="E198"/>
+      <c r="F198"/>
+      <c r="G198"/>
+      <c r="H198"/>
+      <c r="I198"/>
+      <c r="J198"/>
+      <c r="K198"/>
+      <c r="L198"/>
+      <c r="M198"/>
+      <c r="N198"/>
+      <c r="O198"/>
+      <c r="P198"/>
+      <c r="Q198"/>
+      <c r="R198"/>
+      <c r="S198"/>
+      <c r="T198"/>
+    </row>
+    <row r="199" ht="19.5" customHeight="true">
+      <c r="A199" s="10"/>
+      <c r="B199" s="10"/>
+      <c r="C199" s="10"/>
+      <c r="D199"/>
+      <c r="E199"/>
+      <c r="F199"/>
+      <c r="G199"/>
+      <c r="H199"/>
+      <c r="I199"/>
+      <c r="J199"/>
+      <c r="K199"/>
+      <c r="L199"/>
+      <c r="M199"/>
+      <c r="N199"/>
+      <c r="O199"/>
+      <c r="P199"/>
+      <c r="Q199"/>
+      <c r="R199"/>
+      <c r="S199"/>
+      <c r="T199"/>
+    </row>
+    <row r="200" ht="19.5" customHeight="true">
+      <c r="A200" s="10"/>
+      <c r="B200" s="10"/>
+      <c r="C200" s="10"/>
+      <c r="D200"/>
+      <c r="E200"/>
+      <c r="F200"/>
+      <c r="G200"/>
+      <c r="H200"/>
+      <c r="I200"/>
+      <c r="J200"/>
+      <c r="K200"/>
+      <c r="L200"/>
+      <c r="M200"/>
+      <c r="N200"/>
+      <c r="O200"/>
+      <c r="P200"/>
+      <c r="Q200"/>
+      <c r="R200"/>
+      <c r="S200"/>
+      <c r="T200"/>
+    </row>
+    <row r="201" ht="19.5" customHeight="true">
+      <c r="A201" s="10"/>
+      <c r="B201" s="10"/>
+      <c r="C201" s="10"/>
+      <c r="D201"/>
+      <c r="E201"/>
+      <c r="F201"/>
+      <c r="G201"/>
+      <c r="H201"/>
+      <c r="I201"/>
+      <c r="J201"/>
+      <c r="K201"/>
+      <c r="L201"/>
+      <c r="M201"/>
+      <c r="N201"/>
+      <c r="O201"/>
+      <c r="P201"/>
+      <c r="Q201"/>
+      <c r="R201"/>
+      <c r="S201"/>
+      <c r="T201"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultRowHeight="19.5" baseColWidth="14" customHeight="true"/>
+  <cols>
+    <col min="2" max="2" width="43.0" customWidth="true"/>
+    <col min="3" max="3" width="71.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.5" customHeight="true">
+      <c r="A1" t="s" s="12">
+        <v>276</v>
+      </c>
+      <c r="B1" t="s" s="9">
+        <v>277</v>
+      </c>
+      <c r="C1" t="s" s="11">
+        <v>278</v>
+      </c>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+    </row>
+    <row r="2" ht="19.5" customHeight="true">
+      <c r="A2" t="s" s="12">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s" s="9">
+        <v>190</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="true">
+      <c r="A3" s="10"/>
+      <c r="B3" t="s" s="9">
+        <v>198</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="true">
+      <c r="A4" s="10"/>
+      <c r="B4" t="s" s="9">
+        <v>206</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+    </row>
+    <row r="5" ht="19.5" customHeight="true">
+      <c r="A5" s="10"/>
+      <c r="B5" t="s" s="9">
+        <v>214</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="true">
+      <c r="A6" s="10"/>
+      <c r="B6" t="s" s="9">
+        <v>222</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="true">
+      <c r="A7" s="10"/>
+      <c r="B7" t="s" s="9">
+        <v>230</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+    </row>
+    <row r="8" ht="19.5" customHeight="true">
+      <c r="A8" s="10"/>
+      <c r="B8" t="s" s="9">
+        <v>237</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="true">
+      <c r="A9" s="10"/>
+      <c r="B9" t="s" s="9">
+        <v>244</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="true">
+      <c r="A10" s="10"/>
+      <c r="B10" t="s" s="9">
+        <v>250</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="true">
+      <c r="A11" s="10"/>
+      <c r="B11" t="s" s="9">
+        <v>256</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="true">
+      <c r="A12" s="10"/>
+      <c r="B12" t="s" s="9">
+        <v>261</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="true">
+      <c r="A13" s="10"/>
+      <c r="B13" t="s" s="9">
+        <v>266</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="true">
+      <c r="A14" s="10"/>
+      <c r="B14" t="s" s="9">
+        <v>268</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="true">
+      <c r="A15" s="10"/>
+      <c r="B15" t="s" s="9">
+        <v>270</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="true">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16"/>
       <c r="D16"/>
       <c r="E16"/>
@@ -11681,8 +16200,8 @@
       <c r="T16"/>
     </row>
     <row r="17" ht="19.5" customHeight="true">
-      <c r="A17"/>
-      <c r="B17"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17"/>
@@ -11703,8 +16222,8 @@
       <c r="T17"/>
     </row>
     <row r="18" ht="19.5" customHeight="true">
-      <c r="A18"/>
-      <c r="B18"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18"/>
@@ -11725,8 +16244,8 @@
       <c r="T18"/>
     </row>
     <row r="19" ht="19.5" customHeight="true">
-      <c r="A19"/>
-      <c r="B19"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
@@ -11747,8 +16266,8 @@
       <c r="T19"/>
     </row>
     <row r="20" ht="19.5" customHeight="true">
-      <c r="A20"/>
-      <c r="B20"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
@@ -11769,8 +16288,8 @@
       <c r="T20"/>
     </row>
     <row r="21" ht="19.5" customHeight="true">
-      <c r="A21"/>
-      <c r="B21"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
@@ -11791,8 +16310,8 @@
       <c r="T21"/>
     </row>
     <row r="22" ht="19.5" customHeight="true">
-      <c r="A22"/>
-      <c r="B22"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
@@ -11813,8 +16332,8 @@
       <c r="T22"/>
     </row>
     <row r="23" ht="19.5" customHeight="true">
-      <c r="A23"/>
-      <c r="B23"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
@@ -11835,8 +16354,8 @@
       <c r="T23"/>
     </row>
     <row r="24" ht="19.5" customHeight="true">
-      <c r="A24"/>
-      <c r="B24"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
@@ -11857,8 +16376,8 @@
       <c r="T24"/>
     </row>
     <row r="25" ht="19.5" customHeight="true">
-      <c r="A25"/>
-      <c r="B25"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25"/>
@@ -11879,8 +16398,8 @@
       <c r="T25"/>
     </row>
     <row r="26" ht="19.5" customHeight="true">
-      <c r="A26"/>
-      <c r="B26"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -11901,8 +16420,8 @@
       <c r="T26"/>
     </row>
     <row r="27" ht="19.5" customHeight="true">
-      <c r="A27"/>
-      <c r="B27"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -11923,8 +16442,8 @@
       <c r="T27"/>
     </row>
     <row r="28" ht="19.5" customHeight="true">
-      <c r="A28"/>
-      <c r="B28"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -11945,8 +16464,8 @@
       <c r="T28"/>
     </row>
     <row r="29" ht="19.5" customHeight="true">
-      <c r="A29"/>
-      <c r="B29"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -11967,8 +16486,8 @@
       <c r="T29"/>
     </row>
     <row r="30" ht="19.5" customHeight="true">
-      <c r="A30"/>
-      <c r="B30"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
@@ -11989,8 +16508,8 @@
       <c r="T30"/>
     </row>
     <row r="31" ht="19.5" customHeight="true">
-      <c r="A31"/>
-      <c r="B31"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -12011,8 +16530,8 @@
       <c r="T31"/>
     </row>
     <row r="32" ht="19.5" customHeight="true">
-      <c r="A32"/>
-      <c r="B32"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -12033,8 +16552,8 @@
       <c r="T32"/>
     </row>
     <row r="33" ht="19.5" customHeight="true">
-      <c r="A33"/>
-      <c r="B33"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -12055,8 +16574,8 @@
       <c r="T33"/>
     </row>
     <row r="34" ht="19.5" customHeight="true">
-      <c r="A34"/>
-      <c r="B34"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -12077,8 +16596,8 @@
       <c r="T34"/>
     </row>
     <row r="35" ht="19.5" customHeight="true">
-      <c r="A35"/>
-      <c r="B35"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -12099,8 +16618,8 @@
       <c r="T35"/>
     </row>
     <row r="36" ht="19.5" customHeight="true">
-      <c r="A36"/>
-      <c r="B36"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36"/>
@@ -12121,8 +16640,8 @@
       <c r="T36"/>
     </row>
     <row r="37" ht="19.5" customHeight="true">
-      <c r="A37"/>
-      <c r="B37"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
       <c r="C37"/>
       <c r="D37"/>
       <c r="E37"/>
@@ -12143,8 +16662,8 @@
       <c r="T37"/>
     </row>
     <row r="38" ht="19.5" customHeight="true">
-      <c r="A38"/>
-      <c r="B38"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
       <c r="C38"/>
       <c r="D38"/>
       <c r="E38"/>
@@ -12165,8 +16684,8 @@
       <c r="T38"/>
     </row>
     <row r="39" ht="19.5" customHeight="true">
-      <c r="A39"/>
-      <c r="B39"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -12187,8 +16706,8 @@
       <c r="T39"/>
     </row>
     <row r="40" ht="19.5" customHeight="true">
-      <c r="A40"/>
-      <c r="B40"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40"/>
@@ -12209,8 +16728,8 @@
       <c r="T40"/>
     </row>
     <row r="41" ht="19.5" customHeight="true">
-      <c r="A41"/>
-      <c r="B41"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
@@ -12231,8 +16750,8 @@
       <c r="T41"/>
     </row>
     <row r="42" ht="19.5" customHeight="true">
-      <c r="A42"/>
-      <c r="B42"/>
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
@@ -12253,8 +16772,8 @@
       <c r="T42"/>
     </row>
     <row r="43" ht="19.5" customHeight="true">
-      <c r="A43"/>
-      <c r="B43"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
@@ -12275,8 +16794,8 @@
       <c r="T43"/>
     </row>
     <row r="44" ht="19.5" customHeight="true">
-      <c r="A44"/>
-      <c r="B44"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
@@ -12297,8 +16816,8 @@
       <c r="T44"/>
     </row>
     <row r="45" ht="19.5" customHeight="true">
-      <c r="A45"/>
-      <c r="B45"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45"/>
@@ -12319,8 +16838,8 @@
       <c r="T45"/>
     </row>
     <row r="46" ht="19.5" customHeight="true">
-      <c r="A46"/>
-      <c r="B46"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46"/>
@@ -12341,8 +16860,8 @@
       <c r="T46"/>
     </row>
     <row r="47" ht="19.5" customHeight="true">
-      <c r="A47"/>
-      <c r="B47"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47"/>
@@ -12363,8 +16882,8 @@
       <c r="T47"/>
     </row>
     <row r="48" ht="19.5" customHeight="true">
-      <c r="A48"/>
-      <c r="B48"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48"/>
@@ -12385,8 +16904,8 @@
       <c r="T48"/>
     </row>
     <row r="49" ht="19.5" customHeight="true">
-      <c r="A49"/>
-      <c r="B49"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49"/>
@@ -12407,8 +16926,8 @@
       <c r="T49"/>
     </row>
     <row r="50" ht="19.5" customHeight="true">
-      <c r="A50"/>
-      <c r="B50"/>
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50"/>
@@ -12429,8 +16948,8 @@
       <c r="T50"/>
     </row>
     <row r="51" ht="19.5" customHeight="true">
-      <c r="A51"/>
-      <c r="B51"/>
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
       <c r="C51"/>
       <c r="D51"/>
       <c r="E51"/>
@@ -12451,8 +16970,8 @@
       <c r="T51"/>
     </row>
     <row r="52" ht="19.5" customHeight="true">
-      <c r="A52"/>
-      <c r="B52"/>
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
       <c r="C52"/>
       <c r="D52"/>
       <c r="E52"/>
@@ -12473,8 +16992,8 @@
       <c r="T52"/>
     </row>
     <row r="53" ht="19.5" customHeight="true">
-      <c r="A53"/>
-      <c r="B53"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53"/>
@@ -12495,8 +17014,8 @@
       <c r="T53"/>
     </row>
     <row r="54" ht="19.5" customHeight="true">
-      <c r="A54"/>
-      <c r="B54"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
@@ -12517,8 +17036,8 @@
       <c r="T54"/>
     </row>
     <row r="55" ht="19.5" customHeight="true">
-      <c r="A55"/>
-      <c r="B55"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
@@ -12539,8 +17058,8 @@
       <c r="T55"/>
     </row>
     <row r="56" ht="19.5" customHeight="true">
-      <c r="A56"/>
-      <c r="B56"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -12561,8 +17080,8 @@
       <c r="T56"/>
     </row>
     <row r="57" ht="19.5" customHeight="true">
-      <c r="A57"/>
-      <c r="B57"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -12583,8 +17102,8 @@
       <c r="T57"/>
     </row>
     <row r="58" ht="19.5" customHeight="true">
-      <c r="A58"/>
-      <c r="B58"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -12605,8 +17124,8 @@
       <c r="T58"/>
     </row>
     <row r="59" ht="19.5" customHeight="true">
-      <c r="A59"/>
-      <c r="B59"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
       <c r="C59"/>
       <c r="D59"/>
       <c r="E59"/>
@@ -12627,8 +17146,8 @@
       <c r="T59"/>
     </row>
     <row r="60" ht="19.5" customHeight="true">
-      <c r="A60"/>
-      <c r="B60"/>
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
       <c r="C60"/>
       <c r="D60"/>
       <c r="E60"/>
@@ -12649,8 +17168,8 @@
       <c r="T60"/>
     </row>
     <row r="61" ht="19.5" customHeight="true">
-      <c r="A61"/>
-      <c r="B61"/>
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
       <c r="C61"/>
       <c r="D61"/>
       <c r="E61"/>
@@ -12671,8 +17190,8 @@
       <c r="T61"/>
     </row>
     <row r="62" ht="19.5" customHeight="true">
-      <c r="A62"/>
-      <c r="B62"/>
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
       <c r="C62"/>
       <c r="D62"/>
       <c r="E62"/>
@@ -12693,8 +17212,8 @@
       <c r="T62"/>
     </row>
     <row r="63" ht="19.5" customHeight="true">
-      <c r="A63"/>
-      <c r="B63"/>
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
       <c r="C63"/>
       <c r="D63"/>
       <c r="E63"/>
@@ -12715,8 +17234,8 @@
       <c r="T63"/>
     </row>
     <row r="64" ht="19.5" customHeight="true">
-      <c r="A64"/>
-      <c r="B64"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
       <c r="C64"/>
       <c r="D64"/>
       <c r="E64"/>
@@ -12737,8 +17256,8 @@
       <c r="T64"/>
     </row>
     <row r="65" ht="19.5" customHeight="true">
-      <c r="A65"/>
-      <c r="B65"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
       <c r="C65"/>
       <c r="D65"/>
       <c r="E65"/>
@@ -12759,8 +17278,8 @@
       <c r="T65"/>
     </row>
     <row r="66" ht="19.5" customHeight="true">
-      <c r="A66"/>
-      <c r="B66"/>
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
       <c r="C66"/>
       <c r="D66"/>
       <c r="E66"/>
@@ -12781,8 +17300,8 @@
       <c r="T66"/>
     </row>
     <row r="67" ht="19.5" customHeight="true">
-      <c r="A67"/>
-      <c r="B67"/>
+      <c r="A67" s="10"/>
+      <c r="B67" s="10"/>
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67"/>
@@ -12803,8 +17322,8 @@
       <c r="T67"/>
     </row>
     <row r="68" ht="19.5" customHeight="true">
-      <c r="A68"/>
-      <c r="B68"/>
+      <c r="A68" s="10"/>
+      <c r="B68" s="10"/>
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68"/>
@@ -12825,8 +17344,8 @@
       <c r="T68"/>
     </row>
     <row r="69" ht="19.5" customHeight="true">
-      <c r="A69"/>
-      <c r="B69"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69"/>
@@ -12847,8 +17366,8 @@
       <c r="T69"/>
     </row>
     <row r="70" ht="19.5" customHeight="true">
-      <c r="A70"/>
-      <c r="B70"/>
+      <c r="A70" s="10"/>
+      <c r="B70" s="10"/>
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70"/>
@@ -12869,8 +17388,8 @@
       <c r="T70"/>
     </row>
     <row r="71" ht="19.5" customHeight="true">
-      <c r="A71"/>
-      <c r="B71"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="10"/>
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71"/>
@@ -12891,8 +17410,8 @@
       <c r="T71"/>
     </row>
     <row r="72" ht="19.5" customHeight="true">
-      <c r="A72"/>
-      <c r="B72"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72"/>
@@ -12913,8 +17432,8 @@
       <c r="T72"/>
     </row>
     <row r="73" ht="19.5" customHeight="true">
-      <c r="A73"/>
-      <c r="B73"/>
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73"/>
@@ -12935,8 +17454,8 @@
       <c r="T73"/>
     </row>
     <row r="74" ht="19.5" customHeight="true">
-      <c r="A74"/>
-      <c r="B74"/>
+      <c r="A74" s="10"/>
+      <c r="B74" s="10"/>
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74"/>
@@ -12957,8 +17476,8 @@
       <c r="T74"/>
     </row>
     <row r="75" ht="19.5" customHeight="true">
-      <c r="A75"/>
-      <c r="B75"/>
+      <c r="A75" s="10"/>
+      <c r="B75" s="10"/>
       <c r="C75"/>
       <c r="D75"/>
       <c r="E75"/>
@@ -12979,8 +17498,8 @@
       <c r="T75"/>
     </row>
     <row r="76" ht="19.5" customHeight="true">
-      <c r="A76"/>
-      <c r="B76"/>
+      <c r="A76" s="10"/>
+      <c r="B76" s="10"/>
       <c r="C76"/>
       <c r="D76"/>
       <c r="E76"/>
@@ -13001,8 +17520,8 @@
       <c r="T76"/>
     </row>
     <row r="77" ht="19.5" customHeight="true">
-      <c r="A77"/>
-      <c r="B77"/>
+      <c r="A77" s="10"/>
+      <c r="B77" s="10"/>
       <c r="C77"/>
       <c r="D77"/>
       <c r="E77"/>
@@ -13023,8 +17542,8 @@
       <c r="T77"/>
     </row>
     <row r="78" ht="19.5" customHeight="true">
-      <c r="A78"/>
-      <c r="B78"/>
+      <c r="A78" s="10"/>
+      <c r="B78" s="10"/>
       <c r="C78"/>
       <c r="D78"/>
       <c r="E78"/>
@@ -13045,8 +17564,8 @@
       <c r="T78"/>
     </row>
     <row r="79" ht="19.5" customHeight="true">
-      <c r="A79"/>
-      <c r="B79"/>
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
       <c r="C79"/>
       <c r="D79"/>
       <c r="E79"/>
@@ -13067,8 +17586,8 @@
       <c r="T79"/>
     </row>
     <row r="80" ht="19.5" customHeight="true">
-      <c r="A80"/>
-      <c r="B80"/>
+      <c r="A80" s="10"/>
+      <c r="B80" s="10"/>
       <c r="C80"/>
       <c r="D80"/>
       <c r="E80"/>
@@ -13089,8 +17608,8 @@
       <c r="T80"/>
     </row>
     <row r="81" ht="19.5" customHeight="true">
-      <c r="A81"/>
-      <c r="B81"/>
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
       <c r="C81"/>
       <c r="D81"/>
       <c r="E81"/>
@@ -13111,8 +17630,8 @@
       <c r="T81"/>
     </row>
     <row r="82" ht="19.5" customHeight="true">
-      <c r="A82"/>
-      <c r="B82"/>
+      <c r="A82" s="10"/>
+      <c r="B82" s="10"/>
       <c r="C82"/>
       <c r="D82"/>
       <c r="E82"/>
@@ -13133,8 +17652,8 @@
       <c r="T82"/>
     </row>
     <row r="83" ht="19.5" customHeight="true">
-      <c r="A83"/>
-      <c r="B83"/>
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
       <c r="C83"/>
       <c r="D83"/>
       <c r="E83"/>
@@ -13155,8 +17674,8 @@
       <c r="T83"/>
     </row>
     <row r="84" ht="19.5" customHeight="true">
-      <c r="A84"/>
-      <c r="B84"/>
+      <c r="A84" s="10"/>
+      <c r="B84" s="10"/>
       <c r="C84"/>
       <c r="D84"/>
       <c r="E84"/>
@@ -13177,8 +17696,8 @@
       <c r="T84"/>
     </row>
     <row r="85" ht="19.5" customHeight="true">
-      <c r="A85"/>
-      <c r="B85"/>
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
       <c r="C85"/>
       <c r="D85"/>
       <c r="E85"/>
@@ -13199,8 +17718,8 @@
       <c r="T85"/>
     </row>
     <row r="86" ht="19.5" customHeight="true">
-      <c r="A86"/>
-      <c r="B86"/>
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
       <c r="C86"/>
       <c r="D86"/>
       <c r="E86"/>
@@ -13221,8 +17740,8 @@
       <c r="T86"/>
     </row>
     <row r="87" ht="19.5" customHeight="true">
-      <c r="A87"/>
-      <c r="B87"/>
+      <c r="A87" s="10"/>
+      <c r="B87" s="10"/>
       <c r="C87"/>
       <c r="D87"/>
       <c r="E87"/>
@@ -13243,8 +17762,8 @@
       <c r="T87"/>
     </row>
     <row r="88" ht="19.5" customHeight="true">
-      <c r="A88"/>
-      <c r="B88"/>
+      <c r="A88" s="10"/>
+      <c r="B88" s="10"/>
       <c r="C88"/>
       <c r="D88"/>
       <c r="E88"/>
@@ -13265,8 +17784,8 @@
       <c r="T88"/>
     </row>
     <row r="89" ht="19.5" customHeight="true">
-      <c r="A89"/>
-      <c r="B89"/>
+      <c r="A89" s="10"/>
+      <c r="B89" s="10"/>
       <c r="C89"/>
       <c r="D89"/>
       <c r="E89"/>
@@ -13287,8 +17806,8 @@
       <c r="T89"/>
     </row>
     <row r="90" ht="19.5" customHeight="true">
-      <c r="A90"/>
-      <c r="B90"/>
+      <c r="A90" s="10"/>
+      <c r="B90" s="10"/>
       <c r="C90"/>
       <c r="D90"/>
       <c r="E90"/>
@@ -13309,8 +17828,8 @@
       <c r="T90"/>
     </row>
     <row r="91" ht="19.5" customHeight="true">
-      <c r="A91"/>
-      <c r="B91"/>
+      <c r="A91" s="10"/>
+      <c r="B91" s="10"/>
       <c r="C91"/>
       <c r="D91"/>
       <c r="E91"/>
@@ -13331,8 +17850,8 @@
       <c r="T91"/>
     </row>
     <row r="92" ht="19.5" customHeight="true">
-      <c r="A92"/>
-      <c r="B92"/>
+      <c r="A92" s="10"/>
+      <c r="B92" s="10"/>
       <c r="C92"/>
       <c r="D92"/>
       <c r="E92"/>
@@ -13353,8 +17872,8 @@
       <c r="T92"/>
     </row>
     <row r="93" ht="19.5" customHeight="true">
-      <c r="A93"/>
-      <c r="B93"/>
+      <c r="A93" s="10"/>
+      <c r="B93" s="10"/>
       <c r="C93"/>
       <c r="D93"/>
       <c r="E93"/>
@@ -13375,8 +17894,8 @@
       <c r="T93"/>
     </row>
     <row r="94" ht="19.5" customHeight="true">
-      <c r="A94"/>
-      <c r="B94"/>
+      <c r="A94" s="10"/>
+      <c r="B94" s="10"/>
       <c r="C94"/>
       <c r="D94"/>
       <c r="E94"/>
@@ -13397,8 +17916,8 @@
       <c r="T94"/>
     </row>
     <row r="95" ht="19.5" customHeight="true">
-      <c r="A95"/>
-      <c r="B95"/>
+      <c r="A95" s="10"/>
+      <c r="B95" s="10"/>
       <c r="C95"/>
       <c r="D95"/>
       <c r="E95"/>
@@ -13419,8 +17938,8 @@
       <c r="T95"/>
     </row>
     <row r="96" ht="19.5" customHeight="true">
-      <c r="A96"/>
-      <c r="B96"/>
+      <c r="A96" s="10"/>
+      <c r="B96" s="10"/>
       <c r="C96"/>
       <c r="D96"/>
       <c r="E96"/>
@@ -13441,8 +17960,8 @@
       <c r="T96"/>
     </row>
     <row r="97" ht="19.5" customHeight="true">
-      <c r="A97"/>
-      <c r="B97"/>
+      <c r="A97" s="10"/>
+      <c r="B97" s="10"/>
       <c r="C97"/>
       <c r="D97"/>
       <c r="E97"/>
@@ -13463,8 +17982,8 @@
       <c r="T97"/>
     </row>
     <row r="98" ht="19.5" customHeight="true">
-      <c r="A98"/>
-      <c r="B98"/>
+      <c r="A98" s="10"/>
+      <c r="B98" s="10"/>
       <c r="C98"/>
       <c r="D98"/>
       <c r="E98"/>
@@ -13485,8 +18004,8 @@
       <c r="T98"/>
     </row>
     <row r="99" ht="19.5" customHeight="true">
-      <c r="A99"/>
-      <c r="B99"/>
+      <c r="A99" s="10"/>
+      <c r="B99" s="10"/>
       <c r="C99"/>
       <c r="D99"/>
       <c r="E99"/>
@@ -13507,8 +18026,8 @@
       <c r="T99"/>
     </row>
     <row r="100" ht="19.5" customHeight="true">
-      <c r="A100"/>
-      <c r="B100"/>
+      <c r="A100" s="10"/>
+      <c r="B100" s="10"/>
       <c r="C100"/>
       <c r="D100"/>
       <c r="E100"/>
@@ -13529,8 +18048,8 @@
       <c r="T100"/>
     </row>
     <row r="101" ht="19.5" customHeight="true">
-      <c r="A101"/>
-      <c r="B101"/>
+      <c r="A101" s="10"/>
+      <c r="B101" s="10"/>
       <c r="C101"/>
       <c r="D101"/>
       <c r="E101"/>
@@ -13551,8 +18070,8 @@
       <c r="T101"/>
     </row>
     <row r="102" ht="19.5" customHeight="true">
-      <c r="A102"/>
-      <c r="B102"/>
+      <c r="A102" s="10"/>
+      <c r="B102" s="10"/>
       <c r="C102"/>
       <c r="D102"/>
       <c r="E102"/>
@@ -13573,8 +18092,8 @@
       <c r="T102"/>
     </row>
     <row r="103" ht="19.5" customHeight="true">
-      <c r="A103"/>
-      <c r="B103"/>
+      <c r="A103" s="10"/>
+      <c r="B103" s="10"/>
       <c r="C103"/>
       <c r="D103"/>
       <c r="E103"/>
@@ -13595,8 +18114,8 @@
       <c r="T103"/>
     </row>
     <row r="104" ht="19.5" customHeight="true">
-      <c r="A104"/>
-      <c r="B104"/>
+      <c r="A104" s="10"/>
+      <c r="B104" s="10"/>
       <c r="C104"/>
       <c r="D104"/>
       <c r="E104"/>
@@ -13617,8 +18136,8 @@
       <c r="T104"/>
     </row>
     <row r="105" ht="19.5" customHeight="true">
-      <c r="A105"/>
-      <c r="B105"/>
+      <c r="A105" s="10"/>
+      <c r="B105" s="10"/>
       <c r="C105"/>
       <c r="D105"/>
       <c r="E105"/>
@@ -13639,8 +18158,8 @@
       <c r="T105"/>
     </row>
     <row r="106" ht="19.5" customHeight="true">
-      <c r="A106"/>
-      <c r="B106"/>
+      <c r="A106" s="10"/>
+      <c r="B106" s="10"/>
       <c r="C106"/>
       <c r="D106"/>
       <c r="E106"/>
@@ -13661,8 +18180,8 @@
       <c r="T106"/>
     </row>
     <row r="107" ht="19.5" customHeight="true">
-      <c r="A107"/>
-      <c r="B107"/>
+      <c r="A107" s="10"/>
+      <c r="B107" s="10"/>
       <c r="C107"/>
       <c r="D107"/>
       <c r="E107"/>
@@ -13683,8 +18202,8 @@
       <c r="T107"/>
     </row>
     <row r="108" ht="19.5" customHeight="true">
-      <c r="A108"/>
-      <c r="B108"/>
+      <c r="A108" s="10"/>
+      <c r="B108" s="10"/>
       <c r="C108"/>
       <c r="D108"/>
       <c r="E108"/>
@@ -13705,8 +18224,8 @@
       <c r="T108"/>
     </row>
     <row r="109" ht="19.5" customHeight="true">
-      <c r="A109"/>
-      <c r="B109"/>
+      <c r="A109" s="10"/>
+      <c r="B109" s="10"/>
       <c r="C109"/>
       <c r="D109"/>
       <c r="E109"/>
@@ -13727,8 +18246,8 @@
       <c r="T109"/>
     </row>
     <row r="110" ht="19.5" customHeight="true">
-      <c r="A110"/>
-      <c r="B110"/>
+      <c r="A110" s="10"/>
+      <c r="B110" s="10"/>
       <c r="C110"/>
       <c r="D110"/>
       <c r="E110"/>
@@ -13749,8 +18268,8 @@
       <c r="T110"/>
     </row>
     <row r="111" ht="19.5" customHeight="true">
-      <c r="A111"/>
-      <c r="B111"/>
+      <c r="A111" s="10"/>
+      <c r="B111" s="10"/>
       <c r="C111"/>
       <c r="D111"/>
       <c r="E111"/>
@@ -13771,8 +18290,8 @@
       <c r="T111"/>
     </row>
     <row r="112" ht="19.5" customHeight="true">
-      <c r="A112"/>
-      <c r="B112"/>
+      <c r="A112" s="10"/>
+      <c r="B112" s="10"/>
       <c r="C112"/>
       <c r="D112"/>
       <c r="E112"/>
@@ -13793,8 +18312,8 @@
       <c r="T112"/>
     </row>
     <row r="113" ht="19.5" customHeight="true">
-      <c r="A113"/>
-      <c r="B113"/>
+      <c r="A113" s="10"/>
+      <c r="B113" s="10"/>
       <c r="C113"/>
       <c r="D113"/>
       <c r="E113"/>
@@ -13815,8 +18334,8 @@
       <c r="T113"/>
     </row>
     <row r="114" ht="19.5" customHeight="true">
-      <c r="A114"/>
-      <c r="B114"/>
+      <c r="A114" s="10"/>
+      <c r="B114" s="10"/>
       <c r="C114"/>
       <c r="D114"/>
       <c r="E114"/>
@@ -13837,8 +18356,8 @@
       <c r="T114"/>
     </row>
     <row r="115" ht="19.5" customHeight="true">
-      <c r="A115"/>
-      <c r="B115"/>
+      <c r="A115" s="10"/>
+      <c r="B115" s="10"/>
       <c r="C115"/>
       <c r="D115"/>
       <c r="E115"/>
@@ -13859,8 +18378,8 @@
       <c r="T115"/>
     </row>
     <row r="116" ht="19.5" customHeight="true">
-      <c r="A116"/>
-      <c r="B116"/>
+      <c r="A116" s="10"/>
+      <c r="B116" s="10"/>
       <c r="C116"/>
       <c r="D116"/>
       <c r="E116"/>
@@ -13881,8 +18400,8 @@
       <c r="T116"/>
     </row>
     <row r="117" ht="19.5" customHeight="true">
-      <c r="A117"/>
-      <c r="B117"/>
+      <c r="A117" s="10"/>
+      <c r="B117" s="10"/>
       <c r="C117"/>
       <c r="D117"/>
       <c r="E117"/>
@@ -13903,8 +18422,8 @@
       <c r="T117"/>
     </row>
     <row r="118" ht="19.5" customHeight="true">
-      <c r="A118"/>
-      <c r="B118"/>
+      <c r="A118" s="10"/>
+      <c r="B118" s="10"/>
       <c r="C118"/>
       <c r="D118"/>
       <c r="E118"/>
@@ -13925,8 +18444,8 @@
       <c r="T118"/>
     </row>
     <row r="119" ht="19.5" customHeight="true">
-      <c r="A119"/>
-      <c r="B119"/>
+      <c r="A119" s="10"/>
+      <c r="B119" s="10"/>
       <c r="C119"/>
       <c r="D119"/>
       <c r="E119"/>
@@ -13947,8 +18466,8 @@
       <c r="T119"/>
     </row>
     <row r="120" ht="19.5" customHeight="true">
-      <c r="A120"/>
-      <c r="B120"/>
+      <c r="A120" s="10"/>
+      <c r="B120" s="10"/>
       <c r="C120"/>
       <c r="D120"/>
       <c r="E120"/>
@@ -13969,8 +18488,8 @@
       <c r="T120"/>
     </row>
     <row r="121" ht="19.5" customHeight="true">
-      <c r="A121"/>
-      <c r="B121"/>
+      <c r="A121" s="10"/>
+      <c r="B121" s="10"/>
       <c r="C121"/>
       <c r="D121"/>
       <c r="E121"/>
@@ -13991,8 +18510,8 @@
       <c r="T121"/>
     </row>
     <row r="122" ht="19.5" customHeight="true">
-      <c r="A122"/>
-      <c r="B122"/>
+      <c r="A122" s="10"/>
+      <c r="B122" s="10"/>
       <c r="C122"/>
       <c r="D122"/>
       <c r="E122"/>
@@ -14013,8 +18532,8 @@
       <c r="T122"/>
     </row>
     <row r="123" ht="19.5" customHeight="true">
-      <c r="A123"/>
-      <c r="B123"/>
+      <c r="A123" s="10"/>
+      <c r="B123" s="10"/>
       <c r="C123"/>
       <c r="D123"/>
       <c r="E123"/>
@@ -14035,8 +18554,8 @@
       <c r="T123"/>
     </row>
     <row r="124" ht="19.5" customHeight="true">
-      <c r="A124"/>
-      <c r="B124"/>
+      <c r="A124" s="10"/>
+      <c r="B124" s="10"/>
       <c r="C124"/>
       <c r="D124"/>
       <c r="E124"/>
@@ -14057,8 +18576,8 @@
       <c r="T124"/>
     </row>
     <row r="125" ht="19.5" customHeight="true">
-      <c r="A125"/>
-      <c r="B125"/>
+      <c r="A125" s="10"/>
+      <c r="B125" s="10"/>
       <c r="C125"/>
       <c r="D125"/>
       <c r="E125"/>
@@ -14079,8 +18598,8 @@
       <c r="T125"/>
     </row>
     <row r="126" ht="19.5" customHeight="true">
-      <c r="A126"/>
-      <c r="B126"/>
+      <c r="A126" s="10"/>
+      <c r="B126" s="10"/>
       <c r="C126"/>
       <c r="D126"/>
       <c r="E126"/>
@@ -14101,8 +18620,8 @@
       <c r="T126"/>
     </row>
     <row r="127" ht="19.5" customHeight="true">
-      <c r="A127"/>
-      <c r="B127"/>
+      <c r="A127" s="10"/>
+      <c r="B127" s="10"/>
       <c r="C127"/>
       <c r="D127"/>
       <c r="E127"/>
@@ -14123,8 +18642,8 @@
       <c r="T127"/>
     </row>
     <row r="128" ht="19.5" customHeight="true">
-      <c r="A128"/>
-      <c r="B128"/>
+      <c r="A128" s="10"/>
+      <c r="B128" s="10"/>
       <c r="C128"/>
       <c r="D128"/>
       <c r="E128"/>
@@ -14145,8 +18664,8 @@
       <c r="T128"/>
     </row>
     <row r="129" ht="19.5" customHeight="true">
-      <c r="A129"/>
-      <c r="B129"/>
+      <c r="A129" s="10"/>
+      <c r="B129" s="10"/>
       <c r="C129"/>
       <c r="D129"/>
       <c r="E129"/>
@@ -14167,8 +18686,8 @@
       <c r="T129"/>
     </row>
     <row r="130" ht="19.5" customHeight="true">
-      <c r="A130"/>
-      <c r="B130"/>
+      <c r="A130" s="10"/>
+      <c r="B130" s="10"/>
       <c r="C130"/>
       <c r="D130"/>
       <c r="E130"/>
@@ -14189,8 +18708,8 @@
       <c r="T130"/>
     </row>
     <row r="131" ht="19.5" customHeight="true">
-      <c r="A131"/>
-      <c r="B131"/>
+      <c r="A131" s="10"/>
+      <c r="B131" s="10"/>
       <c r="C131"/>
       <c r="D131"/>
       <c r="E131"/>
@@ -14211,8 +18730,8 @@
       <c r="T131"/>
     </row>
     <row r="132" ht="19.5" customHeight="true">
-      <c r="A132"/>
-      <c r="B132"/>
+      <c r="A132" s="10"/>
+      <c r="B132" s="10"/>
       <c r="C132"/>
       <c r="D132"/>
       <c r="E132"/>
@@ -14233,8 +18752,8 @@
       <c r="T132"/>
     </row>
     <row r="133" ht="19.5" customHeight="true">
-      <c r="A133"/>
-      <c r="B133"/>
+      <c r="A133" s="10"/>
+      <c r="B133" s="10"/>
       <c r="C133"/>
       <c r="D133"/>
       <c r="E133"/>
@@ -14255,8 +18774,8 @@
       <c r="T133"/>
     </row>
     <row r="134" ht="19.5" customHeight="true">
-      <c r="A134"/>
-      <c r="B134"/>
+      <c r="A134" s="10"/>
+      <c r="B134" s="10"/>
       <c r="C134"/>
       <c r="D134"/>
       <c r="E134"/>
@@ -14277,8 +18796,8 @@
       <c r="T134"/>
     </row>
     <row r="135" ht="19.5" customHeight="true">
-      <c r="A135"/>
-      <c r="B135"/>
+      <c r="A135" s="10"/>
+      <c r="B135" s="10"/>
       <c r="C135"/>
       <c r="D135"/>
       <c r="E135"/>
@@ -14299,8 +18818,8 @@
       <c r="T135"/>
     </row>
     <row r="136" ht="19.5" customHeight="true">
-      <c r="A136"/>
-      <c r="B136"/>
+      <c r="A136" s="10"/>
+      <c r="B136" s="10"/>
       <c r="C136"/>
       <c r="D136"/>
       <c r="E136"/>
@@ -14321,8 +18840,8 @@
       <c r="T136"/>
     </row>
     <row r="137" ht="19.5" customHeight="true">
-      <c r="A137"/>
-      <c r="B137"/>
+      <c r="A137" s="10"/>
+      <c r="B137" s="10"/>
       <c r="C137"/>
       <c r="D137"/>
       <c r="E137"/>
@@ -14343,8 +18862,8 @@
       <c r="T137"/>
     </row>
     <row r="138" ht="19.5" customHeight="true">
-      <c r="A138"/>
-      <c r="B138"/>
+      <c r="A138" s="10"/>
+      <c r="B138" s="10"/>
       <c r="C138"/>
       <c r="D138"/>
       <c r="E138"/>
@@ -14365,8 +18884,8 @@
       <c r="T138"/>
     </row>
     <row r="139" ht="19.5" customHeight="true">
-      <c r="A139"/>
-      <c r="B139"/>
+      <c r="A139" s="10"/>
+      <c r="B139" s="10"/>
       <c r="C139"/>
       <c r="D139"/>
       <c r="E139"/>
@@ -14387,8 +18906,8 @@
       <c r="T139"/>
     </row>
     <row r="140" ht="19.5" customHeight="true">
-      <c r="A140"/>
-      <c r="B140"/>
+      <c r="A140" s="10"/>
+      <c r="B140" s="10"/>
       <c r="C140"/>
       <c r="D140"/>
       <c r="E140"/>
@@ -14409,8 +18928,8 @@
       <c r="T140"/>
     </row>
     <row r="141" ht="19.5" customHeight="true">
-      <c r="A141"/>
-      <c r="B141"/>
+      <c r="A141" s="10"/>
+      <c r="B141" s="10"/>
       <c r="C141"/>
       <c r="D141"/>
       <c r="E141"/>
@@ -14431,8 +18950,8 @@
       <c r="T141"/>
     </row>
     <row r="142" ht="19.5" customHeight="true">
-      <c r="A142"/>
-      <c r="B142"/>
+      <c r="A142" s="10"/>
+      <c r="B142" s="10"/>
       <c r="C142"/>
       <c r="D142"/>
       <c r="E142"/>
@@ -14453,8 +18972,8 @@
       <c r="T142"/>
     </row>
     <row r="143" ht="19.5" customHeight="true">
-      <c r="A143"/>
-      <c r="B143"/>
+      <c r="A143" s="10"/>
+      <c r="B143" s="10"/>
       <c r="C143"/>
       <c r="D143"/>
       <c r="E143"/>
@@ -14475,8 +18994,8 @@
       <c r="T143"/>
     </row>
     <row r="144" ht="19.5" customHeight="true">
-      <c r="A144"/>
-      <c r="B144"/>
+      <c r="A144" s="10"/>
+      <c r="B144" s="10"/>
       <c r="C144"/>
       <c r="D144"/>
       <c r="E144"/>
@@ -14497,8 +19016,8 @@
       <c r="T144"/>
     </row>
     <row r="145" ht="19.5" customHeight="true">
-      <c r="A145"/>
-      <c r="B145"/>
+      <c r="A145" s="10"/>
+      <c r="B145" s="10"/>
       <c r="C145"/>
       <c r="D145"/>
       <c r="E145"/>
@@ -14519,8 +19038,8 @@
       <c r="T145"/>
     </row>
     <row r="146" ht="19.5" customHeight="true">
-      <c r="A146"/>
-      <c r="B146"/>
+      <c r="A146" s="10"/>
+      <c r="B146" s="10"/>
       <c r="C146"/>
       <c r="D146"/>
       <c r="E146"/>
@@ -14541,8 +19060,8 @@
       <c r="T146"/>
     </row>
     <row r="147" ht="19.5" customHeight="true">
-      <c r="A147"/>
-      <c r="B147"/>
+      <c r="A147" s="10"/>
+      <c r="B147" s="10"/>
       <c r="C147"/>
       <c r="D147"/>
       <c r="E147"/>
@@ -14563,8 +19082,8 @@
       <c r="T147"/>
     </row>
     <row r="148" ht="19.5" customHeight="true">
-      <c r="A148"/>
-      <c r="B148"/>
+      <c r="A148" s="10"/>
+      <c r="B148" s="10"/>
       <c r="C148"/>
       <c r="D148"/>
       <c r="E148"/>
@@ -14585,8 +19104,8 @@
       <c r="T148"/>
     </row>
     <row r="149" ht="19.5" customHeight="true">
-      <c r="A149"/>
-      <c r="B149"/>
+      <c r="A149" s="10"/>
+      <c r="B149" s="10"/>
       <c r="C149"/>
       <c r="D149"/>
       <c r="E149"/>
@@ -14607,8 +19126,8 @@
       <c r="T149"/>
     </row>
     <row r="150" ht="19.5" customHeight="true">
-      <c r="A150"/>
-      <c r="B150"/>
+      <c r="A150" s="10"/>
+      <c r="B150" s="10"/>
       <c r="C150"/>
       <c r="D150"/>
       <c r="E150"/>
@@ -14629,8 +19148,8 @@
       <c r="T150"/>
     </row>
     <row r="151" ht="19.5" customHeight="true">
-      <c r="A151"/>
-      <c r="B151"/>
+      <c r="A151" s="10"/>
+      <c r="B151" s="10"/>
       <c r="C151"/>
       <c r="D151"/>
       <c r="E151"/>
@@ -14651,8 +19170,8 @@
       <c r="T151"/>
     </row>
     <row r="152" ht="19.5" customHeight="true">
-      <c r="A152"/>
-      <c r="B152"/>
+      <c r="A152" s="10"/>
+      <c r="B152" s="10"/>
       <c r="C152"/>
       <c r="D152"/>
       <c r="E152"/>
@@ -14673,8 +19192,8 @@
       <c r="T152"/>
     </row>
     <row r="153" ht="19.5" customHeight="true">
-      <c r="A153"/>
-      <c r="B153"/>
+      <c r="A153" s="10"/>
+      <c r="B153" s="10"/>
       <c r="C153"/>
       <c r="D153"/>
       <c r="E153"/>
@@ -14695,8 +19214,8 @@
       <c r="T153"/>
     </row>
     <row r="154" ht="19.5" customHeight="true">
-      <c r="A154"/>
-      <c r="B154"/>
+      <c r="A154" s="10"/>
+      <c r="B154" s="10"/>
       <c r="C154"/>
       <c r="D154"/>
       <c r="E154"/>
@@ -14717,8 +19236,8 @@
       <c r="T154"/>
     </row>
     <row r="155" ht="19.5" customHeight="true">
-      <c r="A155"/>
-      <c r="B155"/>
+      <c r="A155" s="10"/>
+      <c r="B155" s="10"/>
       <c r="C155"/>
       <c r="D155"/>
       <c r="E155"/>
@@ -14739,8 +19258,8 @@
       <c r="T155"/>
     </row>
     <row r="156" ht="19.5" customHeight="true">
-      <c r="A156"/>
-      <c r="B156"/>
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
       <c r="C156"/>
       <c r="D156"/>
       <c r="E156"/>
@@ -14761,8 +19280,8 @@
       <c r="T156"/>
     </row>
     <row r="157" ht="19.5" customHeight="true">
-      <c r="A157"/>
-      <c r="B157"/>
+      <c r="A157" s="10"/>
+      <c r="B157" s="10"/>
       <c r="C157"/>
       <c r="D157"/>
       <c r="E157"/>
@@ -14783,8 +19302,8 @@
       <c r="T157"/>
     </row>
     <row r="158" ht="19.5" customHeight="true">
-      <c r="A158"/>
-      <c r="B158"/>
+      <c r="A158" s="10"/>
+      <c r="B158" s="10"/>
       <c r="C158"/>
       <c r="D158"/>
       <c r="E158"/>
@@ -14805,8 +19324,8 @@
       <c r="T158"/>
     </row>
     <row r="159" ht="19.5" customHeight="true">
-      <c r="A159"/>
-      <c r="B159"/>
+      <c r="A159" s="10"/>
+      <c r="B159" s="10"/>
       <c r="C159"/>
       <c r="D159"/>
       <c r="E159"/>
@@ -14827,8 +19346,8 @@
       <c r="T159"/>
     </row>
     <row r="160" ht="19.5" customHeight="true">
-      <c r="A160"/>
-      <c r="B160"/>
+      <c r="A160" s="10"/>
+      <c r="B160" s="10"/>
       <c r="C160"/>
       <c r="D160"/>
       <c r="E160"/>
@@ -14849,8 +19368,8 @@
       <c r="T160"/>
     </row>
     <row r="161" ht="19.5" customHeight="true">
-      <c r="A161"/>
-      <c r="B161"/>
+      <c r="A161" s="10"/>
+      <c r="B161" s="10"/>
       <c r="C161"/>
       <c r="D161"/>
       <c r="E161"/>
@@ -14871,8 +19390,8 @@
       <c r="T161"/>
     </row>
     <row r="162" ht="19.5" customHeight="true">
-      <c r="A162"/>
-      <c r="B162"/>
+      <c r="A162" s="10"/>
+      <c r="B162" s="10"/>
       <c r="C162"/>
       <c r="D162"/>
       <c r="E162"/>
@@ -14893,8 +19412,8 @@
       <c r="T162"/>
     </row>
     <row r="163" ht="19.5" customHeight="true">
-      <c r="A163"/>
-      <c r="B163"/>
+      <c r="A163" s="10"/>
+      <c r="B163" s="10"/>
       <c r="C163"/>
       <c r="D163"/>
       <c r="E163"/>
@@ -14915,8 +19434,8 @@
       <c r="T163"/>
     </row>
     <row r="164" ht="19.5" customHeight="true">
-      <c r="A164"/>
-      <c r="B164"/>
+      <c r="A164" s="10"/>
+      <c r="B164" s="10"/>
       <c r="C164"/>
       <c r="D164"/>
       <c r="E164"/>
@@ -14937,8 +19456,8 @@
       <c r="T164"/>
     </row>
     <row r="165" ht="19.5" customHeight="true">
-      <c r="A165"/>
-      <c r="B165"/>
+      <c r="A165" s="10"/>
+      <c r="B165" s="10"/>
       <c r="C165"/>
       <c r="D165"/>
       <c r="E165"/>
@@ -14959,8 +19478,8 @@
       <c r="T165"/>
     </row>
     <row r="166" ht="19.5" customHeight="true">
-      <c r="A166"/>
-      <c r="B166"/>
+      <c r="A166" s="10"/>
+      <c r="B166" s="10"/>
       <c r="C166"/>
       <c r="D166"/>
       <c r="E166"/>
@@ -14981,8 +19500,8 @@
       <c r="T166"/>
     </row>
     <row r="167" ht="19.5" customHeight="true">
-      <c r="A167"/>
-      <c r="B167"/>
+      <c r="A167" s="10"/>
+      <c r="B167" s="10"/>
       <c r="C167"/>
       <c r="D167"/>
       <c r="E167"/>
@@ -15003,8 +19522,8 @@
       <c r="T167"/>
     </row>
     <row r="168" ht="19.5" customHeight="true">
-      <c r="A168"/>
-      <c r="B168"/>
+      <c r="A168" s="10"/>
+      <c r="B168" s="10"/>
       <c r="C168"/>
       <c r="D168"/>
       <c r="E168"/>
@@ -15025,8 +19544,8 @@
       <c r="T168"/>
     </row>
     <row r="169" ht="19.5" customHeight="true">
-      <c r="A169"/>
-      <c r="B169"/>
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
       <c r="C169"/>
       <c r="D169"/>
       <c r="E169"/>
@@ -15047,8 +19566,8 @@
       <c r="T169"/>
     </row>
     <row r="170" ht="19.5" customHeight="true">
-      <c r="A170"/>
-      <c r="B170"/>
+      <c r="A170" s="10"/>
+      <c r="B170" s="10"/>
       <c r="C170"/>
       <c r="D170"/>
       <c r="E170"/>
@@ -15069,8 +19588,8 @@
       <c r="T170"/>
     </row>
     <row r="171" ht="19.5" customHeight="true">
-      <c r="A171"/>
-      <c r="B171"/>
+      <c r="A171" s="10"/>
+      <c r="B171" s="10"/>
       <c r="C171"/>
       <c r="D171"/>
       <c r="E171"/>
@@ -15091,8 +19610,8 @@
       <c r="T171"/>
     </row>
     <row r="172" ht="19.5" customHeight="true">
-      <c r="A172"/>
-      <c r="B172"/>
+      <c r="A172" s="10"/>
+      <c r="B172" s="10"/>
       <c r="C172"/>
       <c r="D172"/>
       <c r="E172"/>
@@ -15113,8 +19632,8 @@
       <c r="T172"/>
     </row>
     <row r="173" ht="19.5" customHeight="true">
-      <c r="A173"/>
-      <c r="B173"/>
+      <c r="A173" s="10"/>
+      <c r="B173" s="10"/>
       <c r="C173"/>
       <c r="D173"/>
       <c r="E173"/>
@@ -15135,8 +19654,8 @@
       <c r="T173"/>
     </row>
     <row r="174" ht="19.5" customHeight="true">
-      <c r="A174"/>
-      <c r="B174"/>
+      <c r="A174" s="10"/>
+      <c r="B174" s="10"/>
       <c r="C174"/>
       <c r="D174"/>
       <c r="E174"/>
@@ -15157,8 +19676,8 @@
       <c r="T174"/>
     </row>
     <row r="175" ht="19.5" customHeight="true">
-      <c r="A175"/>
-      <c r="B175"/>
+      <c r="A175" s="10"/>
+      <c r="B175" s="10"/>
       <c r="C175"/>
       <c r="D175"/>
       <c r="E175"/>
@@ -15179,8 +19698,8 @@
       <c r="T175"/>
     </row>
     <row r="176" ht="19.5" customHeight="true">
-      <c r="A176"/>
-      <c r="B176"/>
+      <c r="A176" s="10"/>
+      <c r="B176" s="10"/>
       <c r="C176"/>
       <c r="D176"/>
       <c r="E176"/>
@@ -15201,8 +19720,8 @@
       <c r="T176"/>
     </row>
     <row r="177" ht="19.5" customHeight="true">
-      <c r="A177"/>
-      <c r="B177"/>
+      <c r="A177" s="10"/>
+      <c r="B177" s="10"/>
       <c r="C177"/>
       <c r="D177"/>
       <c r="E177"/>
@@ -15223,8 +19742,8 @@
       <c r="T177"/>
     </row>
     <row r="178" ht="19.5" customHeight="true">
-      <c r="A178"/>
-      <c r="B178"/>
+      <c r="A178" s="10"/>
+      <c r="B178" s="10"/>
       <c r="C178"/>
       <c r="D178"/>
       <c r="E178"/>
@@ -15245,8 +19764,8 @@
       <c r="T178"/>
     </row>
     <row r="179" ht="19.5" customHeight="true">
-      <c r="A179"/>
-      <c r="B179"/>
+      <c r="A179" s="10"/>
+      <c r="B179" s="10"/>
       <c r="C179"/>
       <c r="D179"/>
       <c r="E179"/>
@@ -15267,8 +19786,8 @@
       <c r="T179"/>
     </row>
     <row r="180" ht="19.5" customHeight="true">
-      <c r="A180"/>
-      <c r="B180"/>
+      <c r="A180" s="10"/>
+      <c r="B180" s="10"/>
       <c r="C180"/>
       <c r="D180"/>
       <c r="E180"/>
@@ -15289,8 +19808,8 @@
       <c r="T180"/>
     </row>
     <row r="181" ht="19.5" customHeight="true">
-      <c r="A181"/>
-      <c r="B181"/>
+      <c r="A181" s="10"/>
+      <c r="B181" s="10"/>
       <c r="C181"/>
       <c r="D181"/>
       <c r="E181"/>
@@ -15311,8 +19830,8 @@
       <c r="T181"/>
     </row>
     <row r="182" ht="19.5" customHeight="true">
-      <c r="A182"/>
-      <c r="B182"/>
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
       <c r="C182"/>
       <c r="D182"/>
       <c r="E182"/>
@@ -15333,8 +19852,8 @@
       <c r="T182"/>
     </row>
     <row r="183" ht="19.5" customHeight="true">
-      <c r="A183"/>
-      <c r="B183"/>
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
       <c r="C183"/>
       <c r="D183"/>
       <c r="E183"/>
@@ -15355,8 +19874,8 @@
       <c r="T183"/>
     </row>
     <row r="184" ht="19.5" customHeight="true">
-      <c r="A184"/>
-      <c r="B184"/>
+      <c r="A184" s="10"/>
+      <c r="B184" s="10"/>
       <c r="C184"/>
       <c r="D184"/>
       <c r="E184"/>
@@ -15377,8 +19896,8 @@
       <c r="T184"/>
     </row>
     <row r="185" ht="19.5" customHeight="true">
-      <c r="A185"/>
-      <c r="B185"/>
+      <c r="A185" s="10"/>
+      <c r="B185" s="10"/>
       <c r="C185"/>
       <c r="D185"/>
       <c r="E185"/>
@@ -15399,8 +19918,8 @@
       <c r="T185"/>
     </row>
     <row r="186" ht="19.5" customHeight="true">
-      <c r="A186"/>
-      <c r="B186"/>
+      <c r="A186" s="10"/>
+      <c r="B186" s="10"/>
       <c r="C186"/>
       <c r="D186"/>
       <c r="E186"/>
@@ -15421,8 +19940,8 @@
       <c r="T186"/>
     </row>
     <row r="187" ht="19.5" customHeight="true">
-      <c r="A187"/>
-      <c r="B187"/>
+      <c r="A187" s="10"/>
+      <c r="B187" s="10"/>
       <c r="C187"/>
       <c r="D187"/>
       <c r="E187"/>
@@ -15443,8 +19962,8 @@
       <c r="T187"/>
     </row>
     <row r="188" ht="19.5" customHeight="true">
-      <c r="A188"/>
-      <c r="B188"/>
+      <c r="A188" s="10"/>
+      <c r="B188" s="10"/>
       <c r="C188"/>
       <c r="D188"/>
       <c r="E188"/>
@@ -15465,8 +19984,8 @@
       <c r="T188"/>
     </row>
     <row r="189" ht="19.5" customHeight="true">
-      <c r="A189"/>
-      <c r="B189"/>
+      <c r="A189" s="10"/>
+      <c r="B189" s="10"/>
       <c r="C189"/>
       <c r="D189"/>
       <c r="E189"/>
@@ -15487,8 +20006,8 @@
       <c r="T189"/>
     </row>
     <row r="190" ht="19.5" customHeight="true">
-      <c r="A190"/>
-      <c r="B190"/>
+      <c r="A190" s="10"/>
+      <c r="B190" s="10"/>
       <c r="C190"/>
       <c r="D190"/>
       <c r="E190"/>
@@ -15509,8 +20028,8 @@
       <c r="T190"/>
     </row>
     <row r="191" ht="19.5" customHeight="true">
-      <c r="A191"/>
-      <c r="B191"/>
+      <c r="A191" s="10"/>
+      <c r="B191" s="10"/>
       <c r="C191"/>
       <c r="D191"/>
       <c r="E191"/>
@@ -15531,8 +20050,8 @@
       <c r="T191"/>
     </row>
     <row r="192" ht="19.5" customHeight="true">
-      <c r="A192"/>
-      <c r="B192"/>
+      <c r="A192" s="10"/>
+      <c r="B192" s="10"/>
       <c r="C192"/>
       <c r="D192"/>
       <c r="E192"/>
@@ -15553,8 +20072,8 @@
       <c r="T192"/>
     </row>
     <row r="193" ht="19.5" customHeight="true">
-      <c r="A193"/>
-      <c r="B193"/>
+      <c r="A193" s="10"/>
+      <c r="B193" s="10"/>
       <c r="C193"/>
       <c r="D193"/>
       <c r="E193"/>
@@ -15575,8 +20094,8 @@
       <c r="T193"/>
     </row>
     <row r="194" ht="19.5" customHeight="true">
-      <c r="A194"/>
-      <c r="B194"/>
+      <c r="A194" s="10"/>
+      <c r="B194" s="10"/>
       <c r="C194"/>
       <c r="D194"/>
       <c r="E194"/>
@@ -15597,8 +20116,8 @@
       <c r="T194"/>
     </row>
     <row r="195" ht="19.5" customHeight="true">
-      <c r="A195"/>
-      <c r="B195"/>
+      <c r="A195" s="10"/>
+      <c r="B195" s="10"/>
       <c r="C195"/>
       <c r="D195"/>
       <c r="E195"/>
@@ -15619,8 +20138,8 @@
       <c r="T195"/>
     </row>
     <row r="196" ht="19.5" customHeight="true">
-      <c r="A196"/>
-      <c r="B196"/>
+      <c r="A196" s="10"/>
+      <c r="B196" s="10"/>
       <c r="C196"/>
       <c r="D196"/>
       <c r="E196"/>
@@ -15641,8 +20160,8 @@
       <c r="T196"/>
     </row>
     <row r="197" ht="19.5" customHeight="true">
-      <c r="A197"/>
-      <c r="B197"/>
+      <c r="A197" s="10"/>
+      <c r="B197" s="10"/>
       <c r="C197"/>
       <c r="D197"/>
       <c r="E197"/>
@@ -15663,8 +20182,8 @@
       <c r="T197"/>
     </row>
     <row r="198" ht="19.5" customHeight="true">
-      <c r="A198"/>
-      <c r="B198"/>
+      <c r="A198" s="10"/>
+      <c r="B198" s="10"/>
       <c r="C198"/>
       <c r="D198"/>
       <c r="E198"/>
@@ -15685,8 +20204,8 @@
       <c r="T198"/>
     </row>
     <row r="199" ht="19.5" customHeight="true">
-      <c r="A199"/>
-      <c r="B199"/>
+      <c r="A199" s="10"/>
+      <c r="B199" s="10"/>
       <c r="C199"/>
       <c r="D199"/>
       <c r="E199"/>
@@ -15707,8 +20226,8 @@
       <c r="T199"/>
     </row>
     <row r="200" ht="19.5" customHeight="true">
-      <c r="A200"/>
-      <c r="B200"/>
+      <c r="A200" s="10"/>
+      <c r="B200" s="10"/>
       <c r="C200"/>
       <c r="D200"/>
       <c r="E200"/>
